--- a/internal/reader/testdata/Example Regatta Input Table.xlsx
+++ b/internal/reader/testdata/Example Regatta Input Table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marcsieger/repos/src/github.com/comagnaw/regattaClock/testdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marcsieger/repos/src/github.com/comagnaw/regattaClock/internal/reader/testdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E45C968-9052-B24D-8485-2A26E4F2C852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66094E1B-9997-8341-8E99-AF89C75EE2B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="1220" windowWidth="23260" windowHeight="14860" xr2:uid="{0452A4D9-4F1C-A84B-A40E-B3DF56268FFE}"/>
+    <workbookView xWindow="2180" yWindow="-24260" windowWidth="35660" windowHeight="14860" xr2:uid="{0452A4D9-4F1C-A84B-A40E-B3DF56268FFE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -179,9 +179,6 @@
     <t>Exhibition</t>
   </si>
   <si>
-    <t>Test Name Regatta Results                                                                                                                                                                                                                                                                   March 13, 2025</t>
-  </si>
-  <si>
     <t>Woodstock</t>
   </si>
   <si>
@@ -238,11 +235,17 @@
   <si>
     <t>Phil</t>
   </si>
+  <si>
+    <t xml:space="preserve">Test Name Regatta Results                                                                                                                                                                                                                                                                   </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+  </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -1180,7 +1183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="217">
+  <cellXfs count="218">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1710,14 +1713,65 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1738,59 +1792,11 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2140,40 +2146,42 @@
     <col min="9" max="9" width="14.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="204" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="204"/>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="204"/>
-      <c r="F1" s="204"/>
-      <c r="G1" s="204"/>
-      <c r="H1" s="204"/>
-      <c r="I1" s="204"/>
-    </row>
-    <row r="2" spans="1:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="204"/>
-      <c r="B2" s="204"/>
-      <c r="C2" s="204"/>
-      <c r="D2" s="204"/>
-      <c r="E2" s="204"/>
-      <c r="F2" s="204"/>
-      <c r="G2" s="204"/>
-      <c r="H2" s="204"/>
-      <c r="I2" s="204"/>
+    <row r="1" spans="1:9" ht="24" x14ac:dyDescent="0.2">
+      <c r="A1" s="206" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="206"/>
+      <c r="C1" s="206"/>
+      <c r="D1" s="206"/>
+      <c r="E1" s="206"/>
+      <c r="F1" s="206"/>
+      <c r="G1" s="206"/>
+      <c r="H1" s="206"/>
+      <c r="I1" s="206"/>
+    </row>
+    <row r="2" spans="1:9" ht="24" x14ac:dyDescent="0.2">
+      <c r="A2" s="217">
+        <v>45729</v>
+      </c>
+      <c r="B2" s="217"/>
+      <c r="C2" s="217"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="217"/>
+      <c r="F2" s="217"/>
+      <c r="G2" s="217"/>
+      <c r="H2" s="217"/>
+      <c r="I2" s="217"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="190"/>
-      <c r="B3" s="191"/>
-      <c r="C3" s="192"/>
-      <c r="D3" s="193"/>
-      <c r="E3" s="194"/>
-      <c r="F3" s="195"/>
-      <c r="G3" s="196"/>
-      <c r="H3" s="197"/>
-      <c r="I3" s="194"/>
+      <c r="A3" s="207"/>
+      <c r="B3" s="208"/>
+      <c r="C3" s="209"/>
+      <c r="D3" s="210"/>
+      <c r="E3" s="211"/>
+      <c r="F3" s="212"/>
+      <c r="G3" s="213"/>
+      <c r="H3" s="214"/>
+      <c r="I3" s="211"/>
     </row>
     <row r="4" spans="1:9" s="2" customFormat="1" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="32" t="s">
@@ -2205,28 +2213,28 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="187">
+      <c r="A5" s="191">
         <v>1</v>
       </c>
       <c r="B5" s="188"/>
       <c r="C5" s="36"/>
       <c r="D5" s="37"/>
       <c r="E5" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="39" t="s">
+      <c r="H5" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="H5" s="40" t="s">
-        <v>50</v>
-      </c>
       <c r="I5" s="40"/>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="187"/>
+      <c r="A6" s="191"/>
       <c r="B6" s="188"/>
       <c r="C6" s="8" t="s">
         <v>9</v>
@@ -2247,7 +2255,7 @@
       <c r="I6" s="43"/>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="187"/>
+      <c r="A7" s="191"/>
       <c r="B7" s="188"/>
       <c r="C7" s="7" t="s">
         <v>11</v>
@@ -2260,7 +2268,7 @@
       <c r="I7" s="149"/>
     </row>
     <row r="8" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="187"/>
+      <c r="A8" s="191"/>
       <c r="B8" s="188"/>
       <c r="C8" s="7" t="s">
         <v>12</v>
@@ -2273,7 +2281,7 @@
       <c r="I8" s="149"/>
     </row>
     <row r="9" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9" s="187"/>
+      <c r="A9" s="191"/>
       <c r="B9" s="188"/>
       <c r="C9" s="29" t="s">
         <v>1</v>
@@ -2286,30 +2294,30 @@
       <c r="I9" s="151"/>
     </row>
     <row r="10" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="187">
+      <c r="A10" s="191">
         <v>2</v>
       </c>
       <c r="B10" s="188"/>
       <c r="C10" s="36"/>
       <c r="D10" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="G10" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="44" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" s="45" t="s">
+      <c r="H10" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="H10" s="46" t="s">
-        <v>55</v>
-      </c>
       <c r="I10" s="152"/>
     </row>
     <row r="11" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A11" s="187"/>
+      <c r="A11" s="191"/>
       <c r="B11" s="188"/>
       <c r="C11" s="8" t="s">
         <v>13</v>
@@ -2332,7 +2340,7 @@
       <c r="I11" s="149"/>
     </row>
     <row r="12" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="187"/>
+      <c r="A12" s="191"/>
       <c r="B12" s="188"/>
       <c r="C12" s="7" t="s">
         <v>11</v>
@@ -2345,7 +2353,7 @@
       <c r="I12" s="149"/>
     </row>
     <row r="13" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="187"/>
+      <c r="A13" s="191"/>
       <c r="B13" s="188"/>
       <c r="C13" s="7" t="s">
         <v>12</v>
@@ -2358,7 +2366,7 @@
       <c r="I13" s="149"/>
     </row>
     <row r="14" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="187"/>
+      <c r="A14" s="191"/>
       <c r="B14" s="188"/>
       <c r="C14" s="29" t="s">
         <v>1</v>
@@ -2371,32 +2379,32 @@
       <c r="I14" s="150"/>
     </row>
     <row r="15" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" s="187">
+      <c r="A15" s="191">
         <v>3</v>
       </c>
       <c r="B15" s="188"/>
       <c r="C15" s="36"/>
       <c r="D15" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="50" t="s">
+      <c r="F15" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="F15" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="G15" s="39" t="s">
+      <c r="H15" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="H15" s="39" t="s">
+      <c r="I15" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="I15" s="51" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="16" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A16" s="187"/>
+      <c r="A16" s="191"/>
       <c r="B16" s="188"/>
       <c r="C16" s="8" t="s">
         <v>15</v>
@@ -2413,7 +2421,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="187"/>
+      <c r="A17" s="191"/>
       <c r="B17" s="188"/>
       <c r="C17" s="7" t="s">
         <v>11</v>
@@ -2426,7 +2434,7 @@
       <c r="I17" s="167"/>
     </row>
     <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="187"/>
+      <c r="A18" s="191"/>
       <c r="B18" s="188"/>
       <c r="C18" s="7" t="s">
         <v>12</v>
@@ -2439,7 +2447,7 @@
       <c r="I18" s="168"/>
     </row>
     <row r="19" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="187"/>
+      <c r="A19" s="191"/>
       <c r="B19" s="188"/>
       <c r="C19" s="29" t="s">
         <v>1</v>
@@ -2452,31 +2460,31 @@
       <c r="I19" s="169"/>
     </row>
     <row r="20" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="187">
+      <c r="A20" s="191">
         <v>4</v>
       </c>
-      <c r="B20" s="199"/>
+      <c r="B20" s="196"/>
       <c r="C20" s="36"/>
       <c r="D20" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="E20" s="50" t="s">
+      <c r="F20" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="F20" s="39" t="s">
+      <c r="G20" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="G20" s="37" t="s">
+      <c r="H20" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="H20" s="40" t="s">
-        <v>65</v>
-      </c>
       <c r="I20" s="40"/>
     </row>
     <row r="21" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A21" s="187"/>
-      <c r="B21" s="199"/>
+      <c r="A21" s="191"/>
+      <c r="B21" s="196"/>
       <c r="C21" s="8" t="s">
         <v>16</v>
       </c>
@@ -2490,8 +2498,8 @@
       <c r="I21" s="43"/>
     </row>
     <row r="22" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" s="187"/>
-      <c r="B22" s="199"/>
+      <c r="A22" s="191"/>
+      <c r="B22" s="196"/>
       <c r="C22" s="7" t="s">
         <v>11</v>
       </c>
@@ -2503,8 +2511,8 @@
       <c r="I22" s="115"/>
     </row>
     <row r="23" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="187"/>
-      <c r="B23" s="199"/>
+      <c r="A23" s="191"/>
+      <c r="B23" s="196"/>
       <c r="C23" s="7" t="s">
         <v>12</v>
       </c>
@@ -2516,8 +2524,8 @@
       <c r="I23" s="115"/>
     </row>
     <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="187"/>
-      <c r="B24" s="199"/>
+      <c r="A24" s="191"/>
+      <c r="B24" s="196"/>
       <c r="C24" s="29" t="s">
         <v>1</v>
       </c>
@@ -2529,7 +2537,7 @@
       <c r="I24" s="116"/>
     </row>
     <row r="25" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A25" s="187">
+      <c r="A25" s="191">
         <v>5</v>
       </c>
       <c r="B25" s="188"/>
@@ -2544,7 +2552,7 @@
       <c r="I25" s="46"/>
     </row>
     <row r="26" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A26" s="187"/>
+      <c r="A26" s="191"/>
       <c r="B26" s="188"/>
       <c r="C26" s="8" t="s">
         <v>18</v>
@@ -2557,7 +2565,7 @@
       <c r="I26" s="48"/>
     </row>
     <row r="27" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A27" s="187"/>
+      <c r="A27" s="191"/>
       <c r="B27" s="188"/>
       <c r="C27" s="7" t="s">
         <v>11</v>
@@ -2570,7 +2578,7 @@
       <c r="I27" s="149"/>
     </row>
     <row r="28" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A28" s="187"/>
+      <c r="A28" s="191"/>
       <c r="B28" s="188"/>
       <c r="C28" s="7" t="s">
         <v>12</v>
@@ -2583,8 +2591,8 @@
       <c r="I28" s="149"/>
     </row>
     <row r="29" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="201"/>
-      <c r="B29" s="202"/>
+      <c r="A29" s="195"/>
+      <c r="B29" s="190"/>
       <c r="C29" s="6" t="s">
         <v>1</v>
       </c>
@@ -2596,10 +2604,10 @@
       <c r="I29" s="153"/>
     </row>
     <row r="30" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A30" s="187">
+      <c r="A30" s="191">
         <v>6</v>
       </c>
-      <c r="B30" s="199"/>
+      <c r="B30" s="196"/>
       <c r="C30" s="71" t="s">
         <v>17</v>
       </c>
@@ -2611,8 +2619,8 @@
       <c r="I30" s="46"/>
     </row>
     <row r="31" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A31" s="187"/>
-      <c r="B31" s="199"/>
+      <c r="A31" s="191"/>
+      <c r="B31" s="196"/>
       <c r="C31" s="13" t="s">
         <v>19</v>
       </c>
@@ -2624,8 +2632,8 @@
       <c r="I31" s="48"/>
     </row>
     <row r="32" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="187"/>
-      <c r="B32" s="199"/>
+      <c r="A32" s="191"/>
+      <c r="B32" s="196"/>
       <c r="C32" s="7" t="s">
         <v>11</v>
       </c>
@@ -2637,8 +2645,8 @@
       <c r="I32" s="149"/>
     </row>
     <row r="33" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="187"/>
-      <c r="B33" s="199"/>
+      <c r="A33" s="191"/>
+      <c r="B33" s="196"/>
       <c r="C33" s="7" t="s">
         <v>12</v>
       </c>
@@ -2650,8 +2658,8 @@
       <c r="I33" s="149"/>
     </row>
     <row r="34" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="187"/>
-      <c r="B34" s="199"/>
+      <c r="A34" s="191"/>
+      <c r="B34" s="196"/>
       <c r="C34" s="31" t="s">
         <v>1</v>
       </c>
@@ -2663,10 +2671,10 @@
       <c r="I34" s="151"/>
     </row>
     <row r="35" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A35" s="189">
+      <c r="A35" s="194">
         <v>7</v>
       </c>
-      <c r="B35" s="198"/>
+      <c r="B35" s="215"/>
       <c r="C35" s="59" t="s">
         <v>20</v>
       </c>
@@ -2678,8 +2686,8 @@
       <c r="I35" s="64"/>
     </row>
     <row r="36" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A36" s="187"/>
-      <c r="B36" s="199"/>
+      <c r="A36" s="191"/>
+      <c r="B36" s="196"/>
       <c r="C36" s="13" t="s">
         <v>18</v>
       </c>
@@ -2691,8 +2699,8 @@
       <c r="I36" s="48"/>
     </row>
     <row r="37" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A37" s="187"/>
-      <c r="B37" s="199"/>
+      <c r="A37" s="191"/>
+      <c r="B37" s="196"/>
       <c r="C37" s="7" t="s">
         <v>11</v>
       </c>
@@ -2704,8 +2712,8 @@
       <c r="I37" s="149"/>
     </row>
     <row r="38" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A38" s="187"/>
-      <c r="B38" s="199"/>
+      <c r="A38" s="191"/>
+      <c r="B38" s="196"/>
       <c r="C38" s="7" t="s">
         <v>12</v>
       </c>
@@ -2717,8 +2725,8 @@
       <c r="I38" s="149"/>
     </row>
     <row r="39" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A39" s="201"/>
-      <c r="B39" s="200"/>
+      <c r="A39" s="195"/>
+      <c r="B39" s="216"/>
       <c r="C39" s="16" t="s">
         <v>1</v>
       </c>
@@ -2730,10 +2738,10 @@
       <c r="I39" s="153"/>
     </row>
     <row r="40" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="187">
+      <c r="A40" s="191">
         <v>8</v>
       </c>
-      <c r="B40" s="199"/>
+      <c r="B40" s="196"/>
       <c r="C40" s="71" t="s">
         <v>20</v>
       </c>
@@ -2745,8 +2753,8 @@
       <c r="I40" s="46"/>
     </row>
     <row r="41" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="187"/>
-      <c r="B41" s="199"/>
+      <c r="A41" s="191"/>
+      <c r="B41" s="196"/>
       <c r="C41" s="13" t="s">
         <v>19</v>
       </c>
@@ -2758,8 +2766,8 @@
       <c r="I41" s="48"/>
     </row>
     <row r="42" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="187"/>
-      <c r="B42" s="199"/>
+      <c r="A42" s="191"/>
+      <c r="B42" s="196"/>
       <c r="C42" s="7" t="s">
         <v>11</v>
       </c>
@@ -2771,8 +2779,8 @@
       <c r="I42" s="149"/>
     </row>
     <row r="43" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A43" s="187"/>
-      <c r="B43" s="199"/>
+      <c r="A43" s="191"/>
+      <c r="B43" s="196"/>
       <c r="C43" s="7" t="s">
         <v>12</v>
       </c>
@@ -2784,8 +2792,8 @@
       <c r="I43" s="149"/>
     </row>
     <row r="44" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A44" s="187"/>
-      <c r="B44" s="199"/>
+      <c r="A44" s="191"/>
+      <c r="B44" s="196"/>
       <c r="C44" s="31" t="s">
         <v>1</v>
       </c>
@@ -2797,10 +2805,10 @@
       <c r="I44" s="150"/>
     </row>
     <row r="45" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A45" s="189">
+      <c r="A45" s="194">
         <v>9</v>
       </c>
-      <c r="B45" s="203"/>
+      <c r="B45" s="189"/>
       <c r="C45" s="68"/>
       <c r="D45" s="69"/>
       <c r="E45" s="62"/>
@@ -2810,7 +2818,7 @@
       <c r="I45" s="70"/>
     </row>
     <row r="46" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A46" s="187"/>
+      <c r="A46" s="191"/>
       <c r="B46" s="188"/>
       <c r="C46" s="8" t="s">
         <v>23</v>
@@ -2823,7 +2831,7 @@
       <c r="I46" s="66"/>
     </row>
     <row r="47" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A47" s="187"/>
+      <c r="A47" s="191"/>
       <c r="B47" s="188"/>
       <c r="C47" s="7" t="s">
         <v>11</v>
@@ -2836,7 +2844,7 @@
       <c r="I47" s="167"/>
     </row>
     <row r="48" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="187"/>
+      <c r="A48" s="191"/>
       <c r="B48" s="188"/>
       <c r="C48" s="7" t="s">
         <v>12</v>
@@ -2849,7 +2857,7 @@
       <c r="I48" s="168"/>
     </row>
     <row r="49" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A49" s="187"/>
+      <c r="A49" s="191"/>
       <c r="B49" s="188"/>
       <c r="C49" s="16" t="s">
         <v>1</v>
@@ -2862,7 +2870,7 @@
       <c r="I49" s="169"/>
     </row>
     <row r="50" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A50" s="187">
+      <c r="A50" s="191">
         <v>10</v>
       </c>
       <c r="B50" s="188"/>
@@ -2877,7 +2885,7 @@
       <c r="I50" s="155"/>
     </row>
     <row r="51" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A51" s="187"/>
+      <c r="A51" s="191"/>
       <c r="B51" s="188"/>
       <c r="C51" s="8"/>
       <c r="D51" s="43"/>
@@ -2888,7 +2896,7 @@
       <c r="I51" s="66"/>
     </row>
     <row r="52" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A52" s="187"/>
+      <c r="A52" s="191"/>
       <c r="B52" s="188"/>
       <c r="C52" s="7" t="s">
         <v>11</v>
@@ -2901,7 +2909,7 @@
       <c r="I52" s="167"/>
     </row>
     <row r="53" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A53" s="187"/>
+      <c r="A53" s="191"/>
       <c r="B53" s="188"/>
       <c r="C53" s="7" t="s">
         <v>12</v>
@@ -2914,7 +2922,7 @@
       <c r="I53" s="168"/>
     </row>
     <row r="54" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="187"/>
+      <c r="A54" s="191"/>
       <c r="B54" s="188"/>
       <c r="C54" s="16" t="s">
         <v>1</v>
@@ -2927,10 +2935,10 @@
       <c r="I54" s="169"/>
     </row>
     <row r="55" spans="1:9" s="3" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A55" s="205">
+      <c r="A55" s="198">
         <v>11</v>
       </c>
-      <c r="B55" s="206"/>
+      <c r="B55" s="197"/>
       <c r="C55" s="36" t="s">
         <v>25</v>
       </c>
@@ -2942,8 +2950,8 @@
       <c r="I55" s="51"/>
     </row>
     <row r="56" spans="1:9" s="3" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A56" s="205"/>
-      <c r="B56" s="206"/>
+      <c r="A56" s="198"/>
+      <c r="B56" s="197"/>
       <c r="C56" s="8" t="s">
         <v>18</v>
       </c>
@@ -2955,8 +2963,8 @@
       <c r="I56" s="43"/>
     </row>
     <row r="57" spans="1:9" s="3" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A57" s="205"/>
-      <c r="B57" s="206"/>
+      <c r="A57" s="198"/>
+      <c r="B57" s="197"/>
       <c r="C57" s="7" t="s">
         <v>11</v>
       </c>
@@ -2968,8 +2976,8 @@
       <c r="I57" s="115"/>
     </row>
     <row r="58" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A58" s="205"/>
-      <c r="B58" s="206"/>
+      <c r="A58" s="198"/>
+      <c r="B58" s="197"/>
       <c r="C58" s="7" t="s">
         <v>12</v>
       </c>
@@ -2981,8 +2989,8 @@
       <c r="I58" s="115"/>
     </row>
     <row r="59" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A59" s="205"/>
-      <c r="B59" s="206"/>
+      <c r="A59" s="198"/>
+      <c r="B59" s="197"/>
       <c r="C59" s="16" t="s">
         <v>1</v>
       </c>
@@ -2994,7 +3002,7 @@
       <c r="I59" s="156"/>
     </row>
     <row r="60" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="187">
+      <c r="A60" s="191">
         <v>12</v>
       </c>
       <c r="B60" s="188"/>
@@ -3009,7 +3017,7 @@
       <c r="I60" s="70"/>
     </row>
     <row r="61" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="187"/>
+      <c r="A61" s="191"/>
       <c r="B61" s="188"/>
       <c r="C61" s="8" t="s">
         <v>19</v>
@@ -3022,7 +3030,7 @@
       <c r="I61" s="43"/>
     </row>
     <row r="62" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="187"/>
+      <c r="A62" s="191"/>
       <c r="B62" s="188"/>
       <c r="C62" s="7" t="s">
         <v>11</v>
@@ -3035,7 +3043,7 @@
       <c r="I62" s="115"/>
     </row>
     <row r="63" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A63" s="187"/>
+      <c r="A63" s="191"/>
       <c r="B63" s="188"/>
       <c r="C63" s="7" t="s">
         <v>12</v>
@@ -3048,7 +3056,7 @@
       <c r="I63" s="115"/>
     </row>
     <row r="64" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A64" s="187"/>
+      <c r="A64" s="191"/>
       <c r="B64" s="188"/>
       <c r="C64" s="16" t="s">
         <v>1</v>
@@ -3061,7 +3069,7 @@
       <c r="I64" s="154"/>
     </row>
     <row r="65" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="187">
+      <c r="A65" s="191">
         <v>13</v>
       </c>
       <c r="B65" s="188"/>
@@ -3076,7 +3084,7 @@
       <c r="I65" s="51"/>
     </row>
     <row r="66" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="187"/>
+      <c r="A66" s="191"/>
       <c r="B66" s="188"/>
       <c r="C66" s="8" t="s">
         <v>18</v>
@@ -3089,7 +3097,7 @@
       <c r="I66" s="43"/>
     </row>
     <row r="67" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="187"/>
+      <c r="A67" s="191"/>
       <c r="B67" s="188"/>
       <c r="C67" s="7" t="s">
         <v>11</v>
@@ -3102,7 +3110,7 @@
       <c r="I67" s="115"/>
     </row>
     <row r="68" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A68" s="187"/>
+      <c r="A68" s="191"/>
       <c r="B68" s="188"/>
       <c r="C68" s="7" t="s">
         <v>12</v>
@@ -3115,7 +3123,7 @@
       <c r="I68" s="115"/>
     </row>
     <row r="69" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A69" s="187"/>
+      <c r="A69" s="191"/>
       <c r="B69" s="188"/>
       <c r="C69" s="16" t="s">
         <v>1</v>
@@ -3128,7 +3136,7 @@
       <c r="I69" s="156"/>
     </row>
     <row r="70" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A70" s="187">
+      <c r="A70" s="191">
         <v>14</v>
       </c>
       <c r="B70" s="188"/>
@@ -3143,7 +3151,7 @@
       <c r="I70" s="51"/>
     </row>
     <row r="71" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A71" s="187"/>
+      <c r="A71" s="191"/>
       <c r="B71" s="188"/>
       <c r="C71" s="8" t="s">
         <v>19</v>
@@ -3156,7 +3164,7 @@
       <c r="I71" s="43"/>
     </row>
     <row r="72" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A72" s="187"/>
+      <c r="A72" s="191"/>
       <c r="B72" s="188"/>
       <c r="C72" s="7" t="s">
         <v>11</v>
@@ -3169,7 +3177,7 @@
       <c r="I72" s="126"/>
     </row>
     <row r="73" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="187"/>
+      <c r="A73" s="191"/>
       <c r="B73" s="188"/>
       <c r="C73" s="7" t="s">
         <v>12</v>
@@ -3182,7 +3190,7 @@
       <c r="I73" s="126"/>
     </row>
     <row r="74" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A74" s="187"/>
+      <c r="A74" s="191"/>
       <c r="B74" s="188"/>
       <c r="C74" s="16" t="s">
         <v>1</v>
@@ -3195,7 +3203,7 @@
       <c r="I74" s="156"/>
     </row>
     <row r="75" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A75" s="187">
+      <c r="A75" s="191">
         <v>15</v>
       </c>
       <c r="B75" s="188"/>
@@ -3210,7 +3218,7 @@
       <c r="I75" s="73"/>
     </row>
     <row r="76" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A76" s="187"/>
+      <c r="A76" s="191"/>
       <c r="B76" s="188"/>
       <c r="C76" s="13" t="s">
         <v>18</v>
@@ -3223,7 +3231,7 @@
       <c r="I76" s="75"/>
     </row>
     <row r="77" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A77" s="187"/>
+      <c r="A77" s="191"/>
       <c r="B77" s="188"/>
       <c r="C77" s="7" t="s">
         <v>11</v>
@@ -3236,7 +3244,7 @@
       <c r="I77" s="115"/>
     </row>
     <row r="78" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A78" s="187"/>
+      <c r="A78" s="191"/>
       <c r="B78" s="188"/>
       <c r="C78" s="7" t="s">
         <v>12</v>
@@ -3249,8 +3257,8 @@
       <c r="I78" s="115"/>
     </row>
     <row r="79" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="201"/>
-      <c r="B79" s="202"/>
+      <c r="A79" s="195"/>
+      <c r="B79" s="190"/>
       <c r="C79" s="16" t="s">
         <v>1</v>
       </c>
@@ -3262,7 +3270,7 @@
       <c r="I79" s="157"/>
     </row>
     <row r="80" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="187">
+      <c r="A80" s="191">
         <v>16</v>
       </c>
       <c r="B80" s="188"/>
@@ -3277,7 +3285,7 @@
       <c r="I80" s="73"/>
     </row>
     <row r="81" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="187"/>
+      <c r="A81" s="191"/>
       <c r="B81" s="188"/>
       <c r="C81" s="13" t="s">
         <v>19</v>
@@ -3290,7 +3298,7 @@
       <c r="I81" s="75"/>
     </row>
     <row r="82" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="187"/>
+      <c r="A82" s="191"/>
       <c r="B82" s="188"/>
       <c r="C82" s="7" t="s">
         <v>11</v>
@@ -3303,7 +3311,7 @@
       <c r="I82" s="115"/>
     </row>
     <row r="83" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A83" s="187"/>
+      <c r="A83" s="191"/>
       <c r="B83" s="188"/>
       <c r="C83" s="7" t="s">
         <v>12</v>
@@ -3316,7 +3324,7 @@
       <c r="I83" s="115"/>
     </row>
     <row r="84" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A84" s="187"/>
+      <c r="A84" s="191"/>
       <c r="B84" s="188"/>
       <c r="C84" s="31" t="s">
         <v>1</v>
@@ -3329,10 +3337,10 @@
       <c r="I84" s="116"/>
     </row>
     <row r="85" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A85" s="189">
+      <c r="A85" s="194">
         <v>17</v>
       </c>
-      <c r="B85" s="203"/>
+      <c r="B85" s="189"/>
       <c r="C85" s="59" t="s">
         <v>28</v>
       </c>
@@ -3344,7 +3352,7 @@
       <c r="I85" s="148"/>
     </row>
     <row r="86" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A86" s="187"/>
+      <c r="A86" s="191"/>
       <c r="B86" s="188"/>
       <c r="C86" s="13" t="s">
         <v>18</v>
@@ -3357,7 +3365,7 @@
       <c r="I86" s="80"/>
     </row>
     <row r="87" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A87" s="187"/>
+      <c r="A87" s="191"/>
       <c r="B87" s="188"/>
       <c r="C87" s="7" t="s">
         <v>11</v>
@@ -3370,7 +3378,7 @@
       <c r="I87" s="115"/>
     </row>
     <row r="88" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="187"/>
+      <c r="A88" s="191"/>
       <c r="B88" s="188"/>
       <c r="C88" s="7" t="s">
         <v>12</v>
@@ -3383,7 +3391,7 @@
       <c r="I88" s="115"/>
     </row>
     <row r="89" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A89" s="187"/>
+      <c r="A89" s="191"/>
       <c r="B89" s="188"/>
       <c r="C89" s="16" t="s">
         <v>1</v>
@@ -3396,7 +3404,7 @@
       <c r="I89" s="156"/>
     </row>
     <row r="90" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A90" s="187">
+      <c r="A90" s="191">
         <v>18</v>
       </c>
       <c r="B90" s="188"/>
@@ -3411,7 +3419,7 @@
       <c r="I90" s="78"/>
     </row>
     <row r="91" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A91" s="187"/>
+      <c r="A91" s="191"/>
       <c r="B91" s="188"/>
       <c r="C91" s="13" t="s">
         <v>19</v>
@@ -3424,7 +3432,7 @@
       <c r="I91" s="80"/>
     </row>
     <row r="92" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A92" s="187"/>
+      <c r="A92" s="191"/>
       <c r="B92" s="188"/>
       <c r="C92" s="7" t="s">
         <v>11</v>
@@ -3437,7 +3445,7 @@
       <c r="I92" s="167"/>
     </row>
     <row r="93" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A93" s="187"/>
+      <c r="A93" s="191"/>
       <c r="B93" s="188"/>
       <c r="C93" s="7" t="s">
         <v>12</v>
@@ -3450,8 +3458,8 @@
       <c r="I93" s="168"/>
     </row>
     <row r="94" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="201"/>
-      <c r="B94" s="202"/>
+      <c r="A94" s="195"/>
+      <c r="B94" s="190"/>
       <c r="C94" s="16" t="s">
         <v>1</v>
       </c>
@@ -3463,7 +3471,7 @@
       <c r="I94" s="169"/>
     </row>
     <row r="95" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A95" s="187">
+      <c r="A95" s="191">
         <v>19</v>
       </c>
       <c r="B95" s="188"/>
@@ -3478,7 +3486,7 @@
       <c r="I95" s="73"/>
     </row>
     <row r="96" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A96" s="187"/>
+      <c r="A96" s="191"/>
       <c r="B96" s="188"/>
       <c r="C96" s="13" t="s">
         <v>18</v>
@@ -3491,7 +3499,7 @@
       <c r="I96" s="75"/>
     </row>
     <row r="97" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A97" s="187"/>
+      <c r="A97" s="191"/>
       <c r="B97" s="188"/>
       <c r="C97" s="7" t="s">
         <v>11</v>
@@ -3504,7 +3512,7 @@
       <c r="I97" s="126"/>
     </row>
     <row r="98" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A98" s="187"/>
+      <c r="A98" s="191"/>
       <c r="B98" s="188"/>
       <c r="C98" s="7" t="s">
         <v>12</v>
@@ -3517,7 +3525,7 @@
       <c r="I98" s="126"/>
     </row>
     <row r="99" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A99" s="187"/>
+      <c r="A99" s="191"/>
       <c r="B99" s="188"/>
       <c r="C99" s="31" t="s">
         <v>1</v>
@@ -3530,10 +3538,10 @@
       <c r="I99" s="116"/>
     </row>
     <row r="100" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="189">
+      <c r="A100" s="194">
         <v>20</v>
       </c>
-      <c r="B100" s="203"/>
+      <c r="B100" s="189"/>
       <c r="C100" s="59" t="s">
         <v>29</v>
       </c>
@@ -3545,7 +3553,7 @@
       <c r="I100" s="82"/>
     </row>
     <row r="101" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="187"/>
+      <c r="A101" s="191"/>
       <c r="B101" s="188"/>
       <c r="C101" s="13" t="s">
         <v>19</v>
@@ -3558,7 +3566,7 @@
       <c r="I101" s="75"/>
     </row>
     <row r="102" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="187"/>
+      <c r="A102" s="191"/>
       <c r="B102" s="188"/>
       <c r="C102" s="7" t="s">
         <v>11</v>
@@ -3571,7 +3579,7 @@
       <c r="I102" s="115"/>
     </row>
     <row r="103" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A103" s="187"/>
+      <c r="A103" s="191"/>
       <c r="B103" s="188"/>
       <c r="C103" s="7" t="s">
         <v>12</v>
@@ -3584,7 +3592,7 @@
       <c r="I103" s="115"/>
     </row>
     <row r="104" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A104" s="187"/>
+      <c r="A104" s="191"/>
       <c r="B104" s="188"/>
       <c r="C104" s="16" t="s">
         <v>1</v>
@@ -3597,7 +3605,7 @@
       <c r="I104" s="154"/>
     </row>
     <row r="105" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A105" s="187">
+      <c r="A105" s="191">
         <v>21</v>
       </c>
       <c r="B105" s="188"/>
@@ -3612,7 +3620,7 @@
       <c r="I105" s="73"/>
     </row>
     <row r="106" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A106" s="187"/>
+      <c r="A106" s="191"/>
       <c r="B106" s="188"/>
       <c r="C106" s="13" t="s">
         <v>18</v>
@@ -3625,7 +3633,7 @@
       <c r="I106" s="75"/>
     </row>
     <row r="107" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A107" s="187"/>
+      <c r="A107" s="191"/>
       <c r="B107" s="188"/>
       <c r="C107" s="7" t="s">
         <v>11</v>
@@ -3638,7 +3646,7 @@
       <c r="I107" s="115"/>
     </row>
     <row r="108" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="187"/>
+      <c r="A108" s="191"/>
       <c r="B108" s="188"/>
       <c r="C108" s="7" t="s">
         <v>12</v>
@@ -3651,8 +3659,8 @@
       <c r="I108" s="115"/>
     </row>
     <row r="109" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A109" s="201"/>
-      <c r="B109" s="202"/>
+      <c r="A109" s="195"/>
+      <c r="B109" s="190"/>
       <c r="C109" s="16" t="s">
         <v>1</v>
       </c>
@@ -3664,7 +3672,7 @@
       <c r="I109" s="156"/>
     </row>
     <row r="110" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A110" s="187">
+      <c r="A110" s="191">
         <v>22</v>
       </c>
       <c r="B110" s="188"/>
@@ -3679,7 +3687,7 @@
       <c r="I110" s="73"/>
     </row>
     <row r="111" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A111" s="187"/>
+      <c r="A111" s="191"/>
       <c r="B111" s="188"/>
       <c r="C111" s="13" t="s">
         <v>19</v>
@@ -3692,7 +3700,7 @@
       <c r="I111" s="83"/>
     </row>
     <row r="112" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A112" s="187"/>
+      <c r="A112" s="191"/>
       <c r="B112" s="188"/>
       <c r="C112" s="7" t="s">
         <v>11</v>
@@ -3705,7 +3713,7 @@
       <c r="I112" s="183"/>
     </row>
     <row r="113" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A113" s="187"/>
+      <c r="A113" s="191"/>
       <c r="B113" s="188"/>
       <c r="C113" s="7" t="s">
         <v>12</v>
@@ -3718,7 +3726,7 @@
       <c r="I113" s="184"/>
     </row>
     <row r="114" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="187"/>
+      <c r="A114" s="191"/>
       <c r="B114" s="188"/>
       <c r="C114" s="31" t="s">
         <v>1</v>
@@ -3731,10 +3739,10 @@
       <c r="I114" s="185"/>
     </row>
     <row r="115" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A115" s="189">
+      <c r="A115" s="194">
         <v>23</v>
       </c>
-      <c r="B115" s="203"/>
+      <c r="B115" s="189"/>
       <c r="C115" s="59" t="s">
         <v>31</v>
       </c>
@@ -3746,7 +3754,7 @@
       <c r="I115" s="186"/>
     </row>
     <row r="116" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A116" s="187"/>
+      <c r="A116" s="191"/>
       <c r="B116" s="188"/>
       <c r="C116" s="13" t="s">
         <v>32</v>
@@ -3759,7 +3767,7 @@
       <c r="I116" s="86"/>
     </row>
     <row r="117" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A117" s="187"/>
+      <c r="A117" s="191"/>
       <c r="B117" s="188"/>
       <c r="C117" s="7" t="s">
         <v>11</v>
@@ -3772,7 +3780,7 @@
       <c r="I117" s="115"/>
     </row>
     <row r="118" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A118" s="187"/>
+      <c r="A118" s="191"/>
       <c r="B118" s="188"/>
       <c r="C118" s="7" t="s">
         <v>12</v>
@@ -3785,8 +3793,8 @@
       <c r="I118" s="115"/>
     </row>
     <row r="119" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A119" s="201"/>
-      <c r="B119" s="202"/>
+      <c r="A119" s="195"/>
+      <c r="B119" s="190"/>
       <c r="C119" s="16" t="s">
         <v>1</v>
       </c>
@@ -3798,7 +3806,7 @@
       <c r="I119" s="154"/>
     </row>
     <row r="120" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="187">
+      <c r="A120" s="191">
         <v>24</v>
       </c>
       <c r="B120" s="188"/>
@@ -3811,7 +3819,7 @@
       <c r="I120" s="118"/>
     </row>
     <row r="121" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="187"/>
+      <c r="A121" s="191"/>
       <c r="B121" s="188"/>
       <c r="C121" s="13" t="s">
         <v>33</v>
@@ -3824,7 +3832,7 @@
       <c r="I121" s="115"/>
     </row>
     <row r="122" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="187"/>
+      <c r="A122" s="191"/>
       <c r="B122" s="188"/>
       <c r="C122" s="7" t="s">
         <v>11</v>
@@ -3837,7 +3845,7 @@
       <c r="I122" s="183"/>
     </row>
     <row r="123" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A123" s="187"/>
+      <c r="A123" s="191"/>
       <c r="B123" s="188"/>
       <c r="C123" s="7" t="s">
         <v>12</v>
@@ -3850,7 +3858,7 @@
       <c r="I123" s="184"/>
     </row>
     <row r="124" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A124" s="187"/>
+      <c r="A124" s="191"/>
       <c r="B124" s="188"/>
       <c r="C124" s="31" t="s">
         <v>1</v>
@@ -3863,10 +3871,10 @@
       <c r="I124" s="185"/>
     </row>
     <row r="125" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A125" s="189">
+      <c r="A125" s="194">
         <v>25</v>
       </c>
-      <c r="B125" s="203"/>
+      <c r="B125" s="189"/>
       <c r="C125" s="59"/>
       <c r="D125" s="60"/>
       <c r="E125" s="60"/>
@@ -3876,7 +3884,7 @@
       <c r="I125" s="121"/>
     </row>
     <row r="126" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A126" s="187"/>
+      <c r="A126" s="191"/>
       <c r="B126" s="188"/>
       <c r="C126" s="13" t="s">
         <v>34</v>
@@ -3889,7 +3897,7 @@
       <c r="I126" s="115"/>
     </row>
     <row r="127" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A127" s="187"/>
+      <c r="A127" s="191"/>
       <c r="B127" s="188"/>
       <c r="C127" s="7" t="s">
         <v>11</v>
@@ -3902,7 +3910,7 @@
       <c r="I127" s="115"/>
     </row>
     <row r="128" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="187"/>
+      <c r="A128" s="191"/>
       <c r="B128" s="188"/>
       <c r="C128" s="7" t="s">
         <v>12</v>
@@ -3915,8 +3923,8 @@
       <c r="I128" s="115"/>
     </row>
     <row r="129" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A129" s="201"/>
-      <c r="B129" s="202"/>
+      <c r="A129" s="195"/>
+      <c r="B129" s="190"/>
       <c r="C129" s="16" t="s">
         <v>1</v>
       </c>
@@ -3928,7 +3936,7 @@
       <c r="I129" s="156"/>
     </row>
     <row r="130" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A130" s="187">
+      <c r="A130" s="191">
         <v>26</v>
       </c>
       <c r="B130" s="188"/>
@@ -3943,7 +3951,7 @@
       <c r="I130" s="118"/>
     </row>
     <row r="131" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A131" s="187"/>
+      <c r="A131" s="191"/>
       <c r="B131" s="188"/>
       <c r="C131" s="13" t="s">
         <v>36</v>
@@ -3956,7 +3964,7 @@
       <c r="I131" s="115"/>
     </row>
     <row r="132" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A132" s="187"/>
+      <c r="A132" s="191"/>
       <c r="B132" s="188"/>
       <c r="C132" s="7" t="s">
         <v>11</v>
@@ -3969,7 +3977,7 @@
       <c r="I132" s="115"/>
     </row>
     <row r="133" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A133" s="187"/>
+      <c r="A133" s="191"/>
       <c r="B133" s="188"/>
       <c r="C133" s="7" t="s">
         <v>12</v>
@@ -3982,7 +3990,7 @@
       <c r="I133" s="115"/>
     </row>
     <row r="134" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="187"/>
+      <c r="A134" s="191"/>
       <c r="B134" s="188"/>
       <c r="C134" s="31" t="s">
         <v>1</v>
@@ -3995,10 +4003,10 @@
       <c r="I134" s="116"/>
     </row>
     <row r="135" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A135" s="189">
+      <c r="A135" s="194">
         <v>27</v>
       </c>
-      <c r="B135" s="203"/>
+      <c r="B135" s="189"/>
       <c r="C135" s="59" t="s">
         <v>35</v>
       </c>
@@ -4010,7 +4018,7 @@
       <c r="I135" s="145"/>
     </row>
     <row r="136" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A136" s="187"/>
+      <c r="A136" s="191"/>
       <c r="B136" s="188"/>
       <c r="C136" s="13" t="s">
         <v>37</v>
@@ -4023,7 +4031,7 @@
       <c r="I136" s="126"/>
     </row>
     <row r="137" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A137" s="187"/>
+      <c r="A137" s="191"/>
       <c r="B137" s="188"/>
       <c r="C137" s="7" t="s">
         <v>11</v>
@@ -4036,7 +4044,7 @@
       <c r="I137" s="126"/>
     </row>
     <row r="138" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A138" s="187"/>
+      <c r="A138" s="191"/>
       <c r="B138" s="188"/>
       <c r="C138" s="7" t="s">
         <v>12</v>
@@ -4049,7 +4057,7 @@
       <c r="I138" s="126"/>
     </row>
     <row r="139" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A139" s="187"/>
+      <c r="A139" s="191"/>
       <c r="B139" s="188"/>
       <c r="C139" s="31" t="s">
         <v>1</v>
@@ -4062,10 +4070,10 @@
       <c r="I139" s="116"/>
     </row>
     <row r="140" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="189">
+      <c r="A140" s="194">
         <v>28</v>
       </c>
-      <c r="B140" s="203"/>
+      <c r="B140" s="189"/>
       <c r="C140" s="68" t="s">
         <v>38</v>
       </c>
@@ -4077,7 +4085,7 @@
       <c r="I140" s="175"/>
     </row>
     <row r="141" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="187"/>
+      <c r="A141" s="191"/>
       <c r="B141" s="188"/>
       <c r="C141" s="8" t="s">
         <v>36</v>
@@ -4090,7 +4098,7 @@
       <c r="I141" s="176"/>
     </row>
     <row r="142" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="187"/>
+      <c r="A142" s="191"/>
       <c r="B142" s="188"/>
       <c r="C142" s="7" t="s">
         <v>11</v>
@@ -4103,7 +4111,7 @@
       <c r="I142" s="115"/>
     </row>
     <row r="143" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A143" s="187"/>
+      <c r="A143" s="191"/>
       <c r="B143" s="188"/>
       <c r="C143" s="7" t="s">
         <v>12</v>
@@ -4116,8 +4124,8 @@
       <c r="I143" s="115"/>
     </row>
     <row r="144" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A144" s="201"/>
-      <c r="B144" s="202"/>
+      <c r="A144" s="195"/>
+      <c r="B144" s="190"/>
       <c r="C144" s="16" t="s">
         <v>1</v>
       </c>
@@ -4129,7 +4137,7 @@
       <c r="I144" s="157"/>
     </row>
     <row r="145" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A145" s="187">
+      <c r="A145" s="191">
         <v>29</v>
       </c>
       <c r="B145" s="188"/>
@@ -4144,7 +4152,7 @@
       <c r="I145" s="118"/>
     </row>
     <row r="146" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A146" s="187"/>
+      <c r="A146" s="191"/>
       <c r="B146" s="188"/>
       <c r="C146" s="88" t="s">
         <v>37</v>
@@ -4157,7 +4165,7 @@
       <c r="I146" s="115"/>
     </row>
     <row r="147" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A147" s="187"/>
+      <c r="A147" s="191"/>
       <c r="B147" s="188"/>
       <c r="C147" s="7" t="s">
         <v>11</v>
@@ -4170,7 +4178,7 @@
       <c r="I147" s="115"/>
     </row>
     <row r="148" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A148" s="187"/>
+      <c r="A148" s="191"/>
       <c r="B148" s="188"/>
       <c r="C148" s="7" t="s">
         <v>12</v>
@@ -4183,7 +4191,7 @@
       <c r="I148" s="115"/>
     </row>
     <row r="149" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A149" s="187"/>
+      <c r="A149" s="191"/>
       <c r="B149" s="188"/>
       <c r="C149" s="31" t="s">
         <v>1</v>
@@ -4196,10 +4204,10 @@
       <c r="I149" s="116"/>
     </row>
     <row r="150" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A150" s="211">
+      <c r="A150" s="203">
         <v>30</v>
       </c>
-      <c r="B150" s="213"/>
+      <c r="B150" s="205"/>
       <c r="C150" s="100" t="s">
         <v>39</v>
       </c>
@@ -4211,8 +4219,8 @@
       <c r="I150" s="134"/>
     </row>
     <row r="151" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A151" s="212"/>
-      <c r="B151" s="214"/>
+      <c r="A151" s="204"/>
+      <c r="B151" s="193"/>
       <c r="C151" s="90" t="s">
         <v>32</v>
       </c>
@@ -4224,8 +4232,8 @@
       <c r="I151" s="92"/>
     </row>
     <row r="152" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A152" s="212"/>
-      <c r="B152" s="214"/>
+      <c r="A152" s="204"/>
+      <c r="B152" s="193"/>
       <c r="C152" s="140" t="s">
         <v>11</v>
       </c>
@@ -4237,7 +4245,7 @@
       <c r="I152" s="142"/>
     </row>
     <row r="153" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A153" s="212"/>
+      <c r="A153" s="204"/>
       <c r="B153" s="188"/>
       <c r="C153" s="141" t="s">
         <v>12</v>
@@ -4250,7 +4258,7 @@
       <c r="I153" s="121"/>
     </row>
     <row r="154" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="212"/>
+      <c r="A154" s="204"/>
       <c r="B154" s="188"/>
       <c r="C154" s="31" t="s">
         <v>1</v>
@@ -4263,10 +4271,10 @@
       <c r="I154" s="116"/>
     </row>
     <row r="155" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="208">
+      <c r="A155" s="200">
         <v>31</v>
       </c>
-      <c r="B155" s="209"/>
+      <c r="B155" s="201"/>
       <c r="C155" s="143" t="s">
         <v>20</v>
       </c>
@@ -4278,8 +4286,8 @@
       <c r="I155" s="139"/>
     </row>
     <row r="156" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="205"/>
-      <c r="B156" s="210"/>
+      <c r="A156" s="198"/>
+      <c r="B156" s="202"/>
       <c r="C156" s="90" t="s">
         <v>32</v>
       </c>
@@ -4291,8 +4299,8 @@
       <c r="I156" s="92"/>
     </row>
     <row r="157" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="205"/>
-      <c r="B157" s="210"/>
+      <c r="A157" s="198"/>
+      <c r="B157" s="202"/>
       <c r="C157" s="140" t="s">
         <v>11</v>
       </c>
@@ -4304,8 +4312,8 @@
       <c r="I157" s="167"/>
     </row>
     <row r="158" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="205"/>
-      <c r="B158" s="207"/>
+      <c r="A158" s="198"/>
+      <c r="B158" s="199"/>
       <c r="C158" s="141" t="s">
         <v>12</v>
       </c>
@@ -4317,8 +4325,8 @@
       <c r="I158" s="168"/>
     </row>
     <row r="159" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="205"/>
-      <c r="B159" s="207"/>
+      <c r="A159" s="198"/>
+      <c r="B159" s="199"/>
       <c r="C159" s="31" t="s">
         <v>1</v>
       </c>
@@ -4330,10 +4338,10 @@
       <c r="I159" s="169"/>
     </row>
     <row r="160" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="187">
+      <c r="A160" s="191">
         <v>32</v>
       </c>
-      <c r="B160" s="203"/>
+      <c r="B160" s="189"/>
       <c r="C160" s="59" t="s">
         <v>25</v>
       </c>
@@ -4345,7 +4353,7 @@
       <c r="I160" s="139"/>
     </row>
     <row r="161" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="187"/>
+      <c r="A161" s="191"/>
       <c r="B161" s="188"/>
       <c r="C161" s="136" t="s">
         <v>32</v>
@@ -4358,7 +4366,7 @@
       <c r="I161" s="92"/>
     </row>
     <row r="162" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="187"/>
+      <c r="A162" s="191"/>
       <c r="B162" s="188"/>
       <c r="C162" s="137" t="s">
         <v>11</v>
@@ -4371,7 +4379,7 @@
       <c r="I162" s="167"/>
     </row>
     <row r="163" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="187"/>
+      <c r="A163" s="191"/>
       <c r="B163" s="188"/>
       <c r="C163" s="7" t="s">
         <v>12</v>
@@ -4384,8 +4392,8 @@
       <c r="I163" s="168"/>
     </row>
     <row r="164" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="187"/>
-      <c r="B164" s="202"/>
+      <c r="A164" s="191"/>
+      <c r="B164" s="190"/>
       <c r="C164" s="16" t="s">
         <v>1</v>
       </c>
@@ -4397,10 +4405,10 @@
       <c r="I164" s="169"/>
     </row>
     <row r="165" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A165" s="205">
+      <c r="A165" s="198">
         <v>33</v>
       </c>
-      <c r="B165" s="207"/>
+      <c r="B165" s="199"/>
       <c r="C165" s="71" t="s">
         <v>26</v>
       </c>
@@ -4412,8 +4420,8 @@
       <c r="I165" s="132"/>
     </row>
     <row r="166" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A166" s="205"/>
-      <c r="B166" s="207"/>
+      <c r="A166" s="198"/>
+      <c r="B166" s="199"/>
       <c r="C166" s="5" t="s">
         <v>32</v>
       </c>
@@ -4425,8 +4433,8 @@
       <c r="I166" s="94"/>
     </row>
     <row r="167" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A167" s="205"/>
-      <c r="B167" s="207"/>
+      <c r="A167" s="198"/>
+      <c r="B167" s="199"/>
       <c r="C167" s="7" t="s">
         <v>11</v>
       </c>
@@ -4438,8 +4446,8 @@
       <c r="I167" s="167"/>
     </row>
     <row r="168" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A168" s="205"/>
-      <c r="B168" s="207"/>
+      <c r="A168" s="198"/>
+      <c r="B168" s="199"/>
       <c r="C168" s="7" t="s">
         <v>12</v>
       </c>
@@ -4451,8 +4459,8 @@
       <c r="I168" s="168"/>
     </row>
     <row r="169" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A169" s="205"/>
-      <c r="B169" s="207"/>
+      <c r="A169" s="198"/>
+      <c r="B169" s="199"/>
       <c r="C169" s="31" t="s">
         <v>1</v>
       </c>
@@ -4464,10 +4472,10 @@
       <c r="I169" s="169"/>
     </row>
     <row r="170" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A170" s="187">
+      <c r="A170" s="191">
         <v>34</v>
       </c>
-      <c r="B170" s="203"/>
+      <c r="B170" s="189"/>
       <c r="C170" s="100" t="s">
         <v>40</v>
       </c>
@@ -4479,7 +4487,7 @@
       <c r="I170" s="172"/>
     </row>
     <row r="171" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A171" s="187"/>
+      <c r="A171" s="191"/>
       <c r="B171" s="188"/>
       <c r="C171" s="90"/>
       <c r="D171" s="97"/>
@@ -4490,7 +4498,7 @@
       <c r="I171" s="99"/>
     </row>
     <row r="172" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A172" s="187"/>
+      <c r="A172" s="191"/>
       <c r="B172" s="188"/>
       <c r="C172" s="7" t="s">
         <v>11</v>
@@ -4503,7 +4511,7 @@
       <c r="I172" s="167"/>
     </row>
     <row r="173" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A173" s="187"/>
+      <c r="A173" s="191"/>
       <c r="B173" s="188"/>
       <c r="C173" s="7" t="s">
         <v>12</v>
@@ -4516,8 +4524,8 @@
       <c r="I173" s="168"/>
     </row>
     <row r="174" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A174" s="201"/>
-      <c r="B174" s="202"/>
+      <c r="A174" s="195"/>
+      <c r="B174" s="190"/>
       <c r="C174" s="16" t="s">
         <v>1</v>
       </c>
@@ -4529,7 +4537,7 @@
       <c r="I174" s="169"/>
     </row>
     <row r="175" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A175" s="187">
+      <c r="A175" s="191">
         <v>35</v>
       </c>
       <c r="B175" s="188"/>
@@ -4544,7 +4552,7 @@
       <c r="I175" s="125"/>
     </row>
     <row r="176" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A176" s="187"/>
+      <c r="A176" s="191"/>
       <c r="B176" s="188"/>
       <c r="C176" s="11"/>
       <c r="D176" s="11"/>
@@ -4555,7 +4563,7 @@
       <c r="I176" s="126"/>
     </row>
     <row r="177" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A177" s="187"/>
+      <c r="A177" s="191"/>
       <c r="B177" s="188"/>
       <c r="C177" s="7" t="s">
         <v>11</v>
@@ -4568,7 +4576,7 @@
       <c r="I177" s="126"/>
     </row>
     <row r="178" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A178" s="187"/>
+      <c r="A178" s="191"/>
       <c r="B178" s="188"/>
       <c r="C178" s="7" t="s">
         <v>12</v>
@@ -4581,7 +4589,7 @@
       <c r="I178" s="126"/>
     </row>
     <row r="179" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A179" s="187"/>
+      <c r="A179" s="191"/>
       <c r="B179" s="188"/>
       <c r="C179" s="31" t="s">
         <v>1</v>
@@ -4594,10 +4602,10 @@
       <c r="I179" s="128"/>
     </row>
     <row r="180" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A180" s="189">
+      <c r="A180" s="194">
         <v>36</v>
       </c>
-      <c r="B180" s="203"/>
+      <c r="B180" s="189"/>
       <c r="C180" s="59" t="s">
         <v>42</v>
       </c>
@@ -4609,7 +4617,7 @@
       <c r="I180" s="175"/>
     </row>
     <row r="181" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A181" s="187"/>
+      <c r="A181" s="191"/>
       <c r="B181" s="188"/>
       <c r="C181" s="13" t="s">
         <v>36</v>
@@ -4622,7 +4630,7 @@
       <c r="I181" s="115"/>
     </row>
     <row r="182" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A182" s="187"/>
+      <c r="A182" s="191"/>
       <c r="B182" s="188"/>
       <c r="C182" s="7" t="s">
         <v>11</v>
@@ -4635,7 +4643,7 @@
       <c r="I182" s="115"/>
     </row>
     <row r="183" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A183" s="187"/>
+      <c r="A183" s="191"/>
       <c r="B183" s="188"/>
       <c r="C183" s="7" t="s">
         <v>12</v>
@@ -4648,8 +4656,8 @@
       <c r="I183" s="115"/>
     </row>
     <row r="184" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A184" s="201"/>
-      <c r="B184" s="202"/>
+      <c r="A184" s="195"/>
+      <c r="B184" s="190"/>
       <c r="C184" s="16" t="s">
         <v>1</v>
       </c>
@@ -4661,7 +4669,7 @@
       <c r="I184" s="154"/>
     </row>
     <row r="185" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A185" s="187">
+      <c r="A185" s="191">
         <v>37</v>
       </c>
       <c r="B185" s="188"/>
@@ -4676,7 +4684,7 @@
       <c r="I185" s="118"/>
     </row>
     <row r="186" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A186" s="187"/>
+      <c r="A186" s="191"/>
       <c r="B186" s="188"/>
       <c r="C186" s="13" t="s">
         <v>37</v>
@@ -4689,7 +4697,7 @@
       <c r="I186" s="115"/>
     </row>
     <row r="187" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A187" s="187"/>
+      <c r="A187" s="191"/>
       <c r="B187" s="188"/>
       <c r="C187" s="7" t="s">
         <v>11</v>
@@ -4702,7 +4710,7 @@
       <c r="I187" s="115"/>
     </row>
     <row r="188" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A188" s="187"/>
+      <c r="A188" s="191"/>
       <c r="B188" s="188"/>
       <c r="C188" s="7" t="s">
         <v>12</v>
@@ -4715,7 +4723,7 @@
       <c r="I188" s="115"/>
     </row>
     <row r="189" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A189" s="187"/>
+      <c r="A189" s="191"/>
       <c r="B189" s="188"/>
       <c r="C189" s="31" t="s">
         <v>1</v>
@@ -4728,10 +4736,10 @@
       <c r="I189" s="120"/>
     </row>
     <row r="190" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A190" s="189">
+      <c r="A190" s="194">
         <v>38</v>
       </c>
-      <c r="B190" s="203"/>
+      <c r="B190" s="189"/>
       <c r="C190" s="59"/>
       <c r="D190" s="123"/>
       <c r="E190" s="123"/>
@@ -4741,7 +4749,7 @@
       <c r="I190" s="124"/>
     </row>
     <row r="191" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A191" s="187"/>
+      <c r="A191" s="191"/>
       <c r="B191" s="188"/>
       <c r="C191" s="13" t="s">
         <v>27</v>
@@ -4754,7 +4762,7 @@
       <c r="I191" s="107"/>
     </row>
     <row r="192" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A192" s="187"/>
+      <c r="A192" s="191"/>
       <c r="B192" s="188"/>
       <c r="C192" s="7" t="s">
         <v>11</v>
@@ -4767,7 +4775,7 @@
       <c r="I192" s="167"/>
     </row>
     <row r="193" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A193" s="187"/>
+      <c r="A193" s="191"/>
       <c r="B193" s="188"/>
       <c r="C193" s="7" t="s">
         <v>12</v>
@@ -4780,7 +4788,7 @@
       <c r="I193" s="168"/>
     </row>
     <row r="194" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A194" s="187"/>
+      <c r="A194" s="191"/>
       <c r="B194" s="188"/>
       <c r="C194" s="31" t="s">
         <v>1</v>
@@ -4793,7 +4801,7 @@
       <c r="I194" s="169"/>
     </row>
     <row r="195" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A195" s="187">
+      <c r="A195" s="191">
         <v>39</v>
       </c>
       <c r="B195" s="188"/>
@@ -4808,7 +4816,7 @@
       <c r="I195" s="121"/>
     </row>
     <row r="196" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A196" s="187"/>
+      <c r="A196" s="191"/>
       <c r="B196" s="188"/>
       <c r="C196" s="11"/>
       <c r="D196" s="11"/>
@@ -4819,7 +4827,7 @@
       <c r="I196" s="115"/>
     </row>
     <row r="197" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A197" s="187"/>
+      <c r="A197" s="191"/>
       <c r="B197" s="188"/>
       <c r="C197" s="7" t="s">
         <v>11</v>
@@ -4832,7 +4840,7 @@
       <c r="I197" s="115"/>
     </row>
     <row r="198" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A198" s="187"/>
+      <c r="A198" s="191"/>
       <c r="B198" s="188"/>
       <c r="C198" s="7" t="s">
         <v>12</v>
@@ -4845,7 +4853,7 @@
       <c r="I198" s="115"/>
     </row>
     <row r="199" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A199" s="187"/>
+      <c r="A199" s="191"/>
       <c r="B199" s="188"/>
       <c r="C199" s="31" t="s">
         <v>1</v>
@@ -4858,7 +4866,7 @@
       <c r="I199" s="116"/>
     </row>
     <row r="200" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A200" s="187">
+      <c r="A200" s="191">
         <v>40</v>
       </c>
       <c r="B200" s="188"/>
@@ -4873,7 +4881,7 @@
       <c r="I200" s="107"/>
     </row>
     <row r="201" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A201" s="187"/>
+      <c r="A201" s="191"/>
       <c r="B201" s="188"/>
       <c r="C201" s="5" t="s">
         <v>32</v>
@@ -4886,7 +4894,7 @@
       <c r="I201" s="109"/>
     </row>
     <row r="202" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A202" s="187"/>
+      <c r="A202" s="191"/>
       <c r="B202" s="188"/>
       <c r="C202" s="7" t="s">
         <v>11</v>
@@ -4899,7 +4907,7 @@
       <c r="I202" s="167"/>
     </row>
     <row r="203" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A203" s="187"/>
+      <c r="A203" s="191"/>
       <c r="B203" s="188"/>
       <c r="C203" s="7" t="s">
         <v>12</v>
@@ -4912,8 +4920,8 @@
       <c r="I203" s="168"/>
     </row>
     <row r="204" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A204" s="201"/>
-      <c r="B204" s="202"/>
+      <c r="A204" s="195"/>
+      <c r="B204" s="190"/>
       <c r="C204" s="16" t="s">
         <v>1</v>
       </c>
@@ -4925,7 +4933,7 @@
       <c r="I204" s="169"/>
     </row>
     <row r="205" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A205" s="187">
+      <c r="A205" s="191">
         <v>41</v>
       </c>
       <c r="B205" s="188"/>
@@ -4940,8 +4948,8 @@
       <c r="I205" s="160"/>
     </row>
     <row r="206" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A206" s="187"/>
-      <c r="B206" s="214"/>
+      <c r="A206" s="191"/>
+      <c r="B206" s="193"/>
       <c r="C206" s="90" t="s">
         <v>32</v>
       </c>
@@ -4953,8 +4961,8 @@
       <c r="I206" s="107"/>
     </row>
     <row r="207" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A207" s="187"/>
-      <c r="B207" s="214"/>
+      <c r="A207" s="191"/>
+      <c r="B207" s="193"/>
       <c r="C207" s="140" t="s">
         <v>11</v>
       </c>
@@ -4966,7 +4974,7 @@
       <c r="I207" s="167"/>
     </row>
     <row r="208" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A208" s="187"/>
+      <c r="A208" s="191"/>
       <c r="B208" s="188"/>
       <c r="C208" s="141" t="s">
         <v>12</v>
@@ -4979,7 +4987,7 @@
       <c r="I208" s="168"/>
     </row>
     <row r="209" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A209" s="187"/>
+      <c r="A209" s="191"/>
       <c r="B209" s="188"/>
       <c r="C209" s="31" t="s">
         <v>1</v>
@@ -4992,10 +5000,10 @@
       <c r="I209" s="169"/>
     </row>
     <row r="210" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A210" s="189">
+      <c r="A210" s="194">
         <v>42</v>
       </c>
-      <c r="B210" s="203"/>
+      <c r="B210" s="189"/>
       <c r="C210" s="100" t="s">
         <v>44</v>
       </c>
@@ -5007,7 +5015,7 @@
       <c r="I210" s="121"/>
     </row>
     <row r="211" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A211" s="187"/>
+      <c r="A211" s="191"/>
       <c r="B211" s="188"/>
       <c r="C211" s="110" t="s">
         <v>36</v>
@@ -5020,7 +5028,7 @@
       <c r="I211" s="115"/>
     </row>
     <row r="212" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A212" s="187"/>
+      <c r="A212" s="191"/>
       <c r="B212" s="188"/>
       <c r="C212" s="7" t="s">
         <v>11</v>
@@ -5033,7 +5041,7 @@
       <c r="I212" s="115"/>
     </row>
     <row r="213" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A213" s="187"/>
+      <c r="A213" s="191"/>
       <c r="B213" s="188"/>
       <c r="C213" s="7" t="s">
         <v>12</v>
@@ -5046,7 +5054,7 @@
       <c r="I213" s="115"/>
     </row>
     <row r="214" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A214" s="187"/>
+      <c r="A214" s="191"/>
       <c r="B214" s="188"/>
       <c r="C214" s="31" t="s">
         <v>1</v>
@@ -5059,10 +5067,10 @@
       <c r="I214" s="116"/>
     </row>
     <row r="215" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A215" s="189">
+      <c r="A215" s="194">
         <v>43</v>
       </c>
-      <c r="B215" s="203"/>
+      <c r="B215" s="189"/>
       <c r="C215" s="100" t="s">
         <v>44</v>
       </c>
@@ -5074,7 +5082,7 @@
       <c r="I215" s="119"/>
     </row>
     <row r="216" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A216" s="187"/>
+      <c r="A216" s="191"/>
       <c r="B216" s="188"/>
       <c r="C216" s="110" t="s">
         <v>37</v>
@@ -5087,7 +5095,7 @@
       <c r="I216" s="181"/>
     </row>
     <row r="217" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A217" s="187"/>
+      <c r="A217" s="191"/>
       <c r="B217" s="188"/>
       <c r="C217" s="7" t="s">
         <v>11</v>
@@ -5100,7 +5108,7 @@
       <c r="I217" s="181"/>
     </row>
     <row r="218" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A218" s="187"/>
+      <c r="A218" s="191"/>
       <c r="B218" s="188"/>
       <c r="C218" s="7" t="s">
         <v>12</v>
@@ -5113,8 +5121,8 @@
       <c r="I218" s="181"/>
     </row>
     <row r="219" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A219" s="201"/>
-      <c r="B219" s="202"/>
+      <c r="A219" s="195"/>
+      <c r="B219" s="190"/>
       <c r="C219" s="16" t="s">
         <v>1</v>
       </c>
@@ -5126,7 +5134,7 @@
       <c r="I219" s="182"/>
     </row>
     <row r="220" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A220" s="187">
+      <c r="A220" s="191">
         <v>44</v>
       </c>
       <c r="B220" s="188"/>
@@ -5141,7 +5149,7 @@
       <c r="I220" s="114"/>
     </row>
     <row r="221" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A221" s="187"/>
+      <c r="A221" s="191"/>
       <c r="B221" s="188"/>
       <c r="C221" s="90" t="s">
         <v>32</v>
@@ -5154,7 +5162,7 @@
       <c r="I221" s="107"/>
     </row>
     <row r="222" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A222" s="187"/>
+      <c r="A222" s="191"/>
       <c r="B222" s="188"/>
       <c r="C222" s="141" t="s">
         <v>11</v>
@@ -5167,7 +5175,7 @@
       <c r="I222" s="167"/>
     </row>
     <row r="223" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A223" s="187"/>
+      <c r="A223" s="191"/>
       <c r="B223" s="188"/>
       <c r="C223" s="7" t="s">
         <v>12</v>
@@ -5180,7 +5188,7 @@
       <c r="I223" s="168"/>
     </row>
     <row r="224" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A224" s="187"/>
+      <c r="A224" s="191"/>
       <c r="B224" s="188"/>
       <c r="C224" s="31" t="s">
         <v>1</v>
@@ -5193,10 +5201,10 @@
       <c r="I224" s="169"/>
     </row>
     <row r="225" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A225" s="215">
+      <c r="A225" s="192">
         <v>45</v>
       </c>
-      <c r="B225" s="203"/>
+      <c r="B225" s="189"/>
       <c r="C225" s="4"/>
       <c r="D225" s="23"/>
       <c r="E225" s="23"/>
@@ -5206,7 +5214,7 @@
       <c r="I225" s="117"/>
     </row>
     <row r="226" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A226" s="216"/>
+      <c r="A226" s="187"/>
       <c r="B226" s="188"/>
       <c r="C226" s="11"/>
       <c r="D226" s="10"/>
@@ -5217,7 +5225,7 @@
       <c r="I226" s="14"/>
     </row>
     <row r="227" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A227" s="216"/>
+      <c r="A227" s="187"/>
       <c r="B227" s="188"/>
       <c r="C227" s="7" t="s">
         <v>11</v>
@@ -5230,7 +5238,7 @@
       <c r="I227" s="14"/>
     </row>
     <row r="228" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A228" s="216"/>
+      <c r="A228" s="187"/>
       <c r="B228" s="188"/>
       <c r="C228" s="7" t="s">
         <v>12</v>
@@ -5243,7 +5251,7 @@
       <c r="I228" s="14"/>
     </row>
     <row r="229" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A229" s="216"/>
+      <c r="A229" s="187"/>
       <c r="B229" s="188"/>
       <c r="C229" s="16" t="s">
         <v>1</v>
@@ -5256,7 +5264,7 @@
       <c r="I229" s="5"/>
     </row>
     <row r="230" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A230" s="216">
+      <c r="A230" s="187">
         <v>46</v>
       </c>
       <c r="B230" s="188"/>
@@ -5269,7 +5277,7 @@
       <c r="I230" s="20"/>
     </row>
     <row r="231" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A231" s="216"/>
+      <c r="A231" s="187"/>
       <c r="B231" s="188"/>
       <c r="C231" s="11"/>
       <c r="D231" s="11"/>
@@ -5280,7 +5288,7 @@
       <c r="I231" s="11"/>
     </row>
     <row r="232" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A232" s="216"/>
+      <c r="A232" s="187"/>
       <c r="B232" s="188"/>
       <c r="C232" s="7" t="s">
         <v>11</v>
@@ -5293,7 +5301,7 @@
       <c r="I232" s="11"/>
     </row>
     <row r="233" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A233" s="216"/>
+      <c r="A233" s="187"/>
       <c r="B233" s="188"/>
       <c r="C233" s="7" t="s">
         <v>12</v>
@@ -5306,7 +5314,7 @@
       <c r="I233" s="11"/>
     </row>
     <row r="234" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A234" s="216"/>
+      <c r="A234" s="187"/>
       <c r="B234" s="188"/>
       <c r="C234" s="16" t="s">
         <v>1</v>
@@ -5319,7 +5327,7 @@
       <c r="I234" s="18"/>
     </row>
     <row r="235" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A235" s="216">
+      <c r="A235" s="187">
         <v>47</v>
       </c>
       <c r="B235" s="188"/>
@@ -5332,7 +5340,7 @@
       <c r="I235" s="20"/>
     </row>
     <row r="236" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A236" s="216"/>
+      <c r="A236" s="187"/>
       <c r="B236" s="188"/>
       <c r="C236" s="11"/>
       <c r="D236" s="11"/>
@@ -5343,7 +5351,7 @@
       <c r="I236" s="11"/>
     </row>
     <row r="237" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A237" s="216"/>
+      <c r="A237" s="187"/>
       <c r="B237" s="188"/>
       <c r="C237" s="7" t="s">
         <v>11</v>
@@ -5356,7 +5364,7 @@
       <c r="I237" s="11"/>
     </row>
     <row r="238" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A238" s="216"/>
+      <c r="A238" s="187"/>
       <c r="B238" s="188"/>
       <c r="C238" s="7" t="s">
         <v>12</v>
@@ -5369,7 +5377,7 @@
       <c r="I238" s="11"/>
     </row>
     <row r="239" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A239" s="216"/>
+      <c r="A239" s="187"/>
       <c r="B239" s="188"/>
       <c r="C239" s="16" t="s">
         <v>1</v>
@@ -5382,7 +5390,7 @@
       <c r="I239" s="5"/>
     </row>
     <row r="240" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A240" s="216">
+      <c r="A240" s="187">
         <v>48</v>
       </c>
       <c r="B240" s="188"/>
@@ -5395,7 +5403,7 @@
       <c r="I240" s="21"/>
     </row>
     <row r="241" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A241" s="216"/>
+      <c r="A241" s="187"/>
       <c r="B241" s="188"/>
       <c r="C241" s="11"/>
       <c r="D241" s="11"/>
@@ -5406,7 +5414,7 @@
       <c r="I241" s="10"/>
     </row>
     <row r="242" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A242" s="216"/>
+      <c r="A242" s="187"/>
       <c r="B242" s="188"/>
       <c r="C242" s="7" t="s">
         <v>11</v>
@@ -5419,7 +5427,7 @@
       <c r="I242" s="10"/>
     </row>
     <row r="243" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A243" s="216"/>
+      <c r="A243" s="187"/>
       <c r="B243" s="188"/>
       <c r="C243" s="7" t="s">
         <v>12</v>
@@ -5432,7 +5440,7 @@
       <c r="I243" s="10"/>
     </row>
     <row r="244" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A244" s="216"/>
+      <c r="A244" s="187"/>
       <c r="B244" s="188"/>
       <c r="C244" s="16" t="s">
         <v>1</v>
@@ -5445,7 +5453,7 @@
       <c r="I244" s="18"/>
     </row>
     <row r="245" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A245" s="216">
+      <c r="A245" s="187">
         <v>49</v>
       </c>
       <c r="B245" s="188"/>
@@ -5458,7 +5466,7 @@
       <c r="I245" s="20"/>
     </row>
     <row r="246" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A246" s="216"/>
+      <c r="A246" s="187"/>
       <c r="B246" s="188"/>
       <c r="C246" s="11"/>
       <c r="D246" s="15"/>
@@ -5469,7 +5477,7 @@
       <c r="I246" s="11"/>
     </row>
     <row r="247" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A247" s="216"/>
+      <c r="A247" s="187"/>
       <c r="B247" s="188"/>
       <c r="C247" s="7" t="s">
         <v>11</v>
@@ -5482,7 +5490,7 @@
       <c r="I247" s="11"/>
     </row>
     <row r="248" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A248" s="216"/>
+      <c r="A248" s="187"/>
       <c r="B248" s="188"/>
       <c r="C248" s="7" t="s">
         <v>12</v>
@@ -5495,7 +5503,7 @@
       <c r="I248" s="11"/>
     </row>
     <row r="249" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A249" s="216"/>
+      <c r="A249" s="187"/>
       <c r="B249" s="188"/>
       <c r="C249" s="16" t="s">
         <v>1</v>
@@ -5508,7 +5516,7 @@
       <c r="I249" s="18"/>
     </row>
     <row r="250" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A250" s="216">
+      <c r="A250" s="187">
         <v>50</v>
       </c>
       <c r="B250" s="188"/>
@@ -5521,7 +5529,7 @@
       <c r="I250" s="20"/>
     </row>
     <row r="251" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A251" s="216"/>
+      <c r="A251" s="187"/>
       <c r="B251" s="188"/>
       <c r="C251" s="11"/>
       <c r="D251" s="11"/>
@@ -5532,7 +5540,7 @@
       <c r="I251" s="11"/>
     </row>
     <row r="252" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A252" s="216"/>
+      <c r="A252" s="187"/>
       <c r="B252" s="188"/>
       <c r="C252" s="7" t="s">
         <v>11</v>
@@ -5545,7 +5553,7 @@
       <c r="I252" s="11"/>
     </row>
     <row r="253" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A253" s="216"/>
+      <c r="A253" s="187"/>
       <c r="B253" s="188"/>
       <c r="C253" s="7" t="s">
         <v>12</v>
@@ -5558,7 +5566,7 @@
       <c r="I253" s="11"/>
     </row>
     <row r="254" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A254" s="216"/>
+      <c r="A254" s="187"/>
       <c r="B254" s="188"/>
       <c r="C254" s="16" t="s">
         <v>1</v>
@@ -5571,7 +5579,7 @@
       <c r="I254" s="12"/>
     </row>
     <row r="255" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A255" s="216">
+      <c r="A255" s="187">
         <v>51</v>
       </c>
       <c r="B255" s="188"/>
@@ -5584,7 +5592,7 @@
       <c r="I255" s="20"/>
     </row>
     <row r="256" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A256" s="216"/>
+      <c r="A256" s="187"/>
       <c r="B256" s="188"/>
       <c r="C256" s="11"/>
       <c r="D256" s="11"/>
@@ -5595,7 +5603,7 @@
       <c r="I256" s="11"/>
     </row>
     <row r="257" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A257" s="216"/>
+      <c r="A257" s="187"/>
       <c r="B257" s="188"/>
       <c r="C257" s="7" t="s">
         <v>11</v>
@@ -5608,7 +5616,7 @@
       <c r="I257" s="11"/>
     </row>
     <row r="258" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A258" s="216"/>
+      <c r="A258" s="187"/>
       <c r="B258" s="188"/>
       <c r="C258" s="7" t="s">
         <v>12</v>
@@ -5621,7 +5629,7 @@
       <c r="I258" s="11"/>
     </row>
     <row r="259" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A259" s="216"/>
+      <c r="A259" s="187"/>
       <c r="B259" s="188"/>
       <c r="C259" s="16" t="s">
         <v>1</v>
@@ -5634,7 +5642,7 @@
       <c r="I259" s="5"/>
     </row>
     <row r="260" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A260" s="216">
+      <c r="A260" s="187">
         <v>52</v>
       </c>
       <c r="B260" s="188"/>
@@ -5647,7 +5655,7 @@
       <c r="I260" s="20"/>
     </row>
     <row r="261" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A261" s="216"/>
+      <c r="A261" s="187"/>
       <c r="B261" s="188"/>
       <c r="C261" s="11"/>
       <c r="D261" s="11"/>
@@ -5658,7 +5666,7 @@
       <c r="I261" s="11"/>
     </row>
     <row r="262" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A262" s="216"/>
+      <c r="A262" s="187"/>
       <c r="B262" s="188"/>
       <c r="C262" s="7" t="s">
         <v>11</v>
@@ -5671,7 +5679,7 @@
       <c r="I262" s="11"/>
     </row>
     <row r="263" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A263" s="216"/>
+      <c r="A263" s="187"/>
       <c r="B263" s="188"/>
       <c r="C263" s="7" t="s">
         <v>12</v>
@@ -5684,7 +5692,7 @@
       <c r="I263" s="11"/>
     </row>
     <row r="264" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A264" s="216"/>
+      <c r="A264" s="187"/>
       <c r="B264" s="188"/>
       <c r="C264" s="16" t="s">
         <v>1</v>
@@ -5697,7 +5705,7 @@
       <c r="I264" s="5"/>
     </row>
     <row r="265" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A265" s="216">
+      <c r="A265" s="187">
         <v>53</v>
       </c>
       <c r="B265" s="188"/>
@@ -5710,7 +5718,7 @@
       <c r="I265" s="21"/>
     </row>
     <row r="266" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A266" s="216"/>
+      <c r="A266" s="187"/>
       <c r="B266" s="188"/>
       <c r="C266" s="11"/>
       <c r="D266" s="10"/>
@@ -5721,7 +5729,7 @@
       <c r="I266" s="10"/>
     </row>
     <row r="267" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A267" s="216"/>
+      <c r="A267" s="187"/>
       <c r="B267" s="188"/>
       <c r="C267" s="7" t="s">
         <v>11</v>
@@ -5734,7 +5742,7 @@
       <c r="I267" s="10"/>
     </row>
     <row r="268" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A268" s="216"/>
+      <c r="A268" s="187"/>
       <c r="B268" s="188"/>
       <c r="C268" s="7" t="s">
         <v>12</v>
@@ -5747,7 +5755,7 @@
       <c r="I268" s="10"/>
     </row>
     <row r="269" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A269" s="216"/>
+      <c r="A269" s="187"/>
       <c r="B269" s="188"/>
       <c r="C269" s="16" t="s">
         <v>1</v>
@@ -5760,7 +5768,7 @@
       <c r="I269" s="5"/>
     </row>
     <row r="270" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A270" s="216">
+      <c r="A270" s="187">
         <v>54</v>
       </c>
       <c r="B270" s="188"/>
@@ -5773,7 +5781,7 @@
       <c r="I270" s="20"/>
     </row>
     <row r="271" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A271" s="216"/>
+      <c r="A271" s="187"/>
       <c r="B271" s="188"/>
       <c r="C271" s="11"/>
       <c r="D271" s="10"/>
@@ -5784,7 +5792,7 @@
       <c r="I271" s="11"/>
     </row>
     <row r="272" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A272" s="216"/>
+      <c r="A272" s="187"/>
       <c r="B272" s="188"/>
       <c r="C272" s="7" t="s">
         <v>11</v>
@@ -5797,7 +5805,7 @@
       <c r="I272" s="11"/>
     </row>
     <row r="273" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A273" s="216"/>
+      <c r="A273" s="187"/>
       <c r="B273" s="188"/>
       <c r="C273" s="7" t="s">
         <v>12</v>
@@ -5810,7 +5818,7 @@
       <c r="I273" s="11"/>
     </row>
     <row r="274" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A274" s="216"/>
+      <c r="A274" s="187"/>
       <c r="B274" s="188"/>
       <c r="C274" s="16" t="s">
         <v>1</v>
@@ -5823,7 +5831,7 @@
       <c r="I274" s="12"/>
     </row>
     <row r="275" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A275" s="216">
+      <c r="A275" s="187">
         <v>55</v>
       </c>
       <c r="B275" s="188"/>
@@ -5836,7 +5844,7 @@
       <c r="I275" s="20"/>
     </row>
     <row r="276" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A276" s="216"/>
+      <c r="A276" s="187"/>
       <c r="B276" s="188"/>
       <c r="C276" s="11"/>
       <c r="D276" s="11"/>
@@ -5847,7 +5855,7 @@
       <c r="I276" s="11"/>
     </row>
     <row r="277" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A277" s="216"/>
+      <c r="A277" s="187"/>
       <c r="B277" s="188"/>
       <c r="C277" s="7" t="s">
         <v>11</v>
@@ -5860,7 +5868,7 @@
       <c r="I277" s="11"/>
     </row>
     <row r="278" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A278" s="216"/>
+      <c r="A278" s="187"/>
       <c r="B278" s="188"/>
       <c r="C278" s="7" t="s">
         <v>12</v>
@@ -5873,7 +5881,7 @@
       <c r="I278" s="11"/>
     </row>
     <row r="279" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A279" s="216"/>
+      <c r="A279" s="187"/>
       <c r="B279" s="188"/>
       <c r="C279" s="16" t="s">
         <v>1</v>
@@ -5886,7 +5894,7 @@
       <c r="I279" s="5"/>
     </row>
     <row r="280" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A280" s="216">
+      <c r="A280" s="187">
         <v>56</v>
       </c>
       <c r="B280" s="188"/>
@@ -5899,7 +5907,7 @@
       <c r="I280" s="20"/>
     </row>
     <row r="281" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A281" s="216"/>
+      <c r="A281" s="187"/>
       <c r="B281" s="188"/>
       <c r="C281" s="11"/>
       <c r="D281" s="11"/>
@@ -5910,7 +5918,7 @@
       <c r="I281" s="11"/>
     </row>
     <row r="282" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A282" s="216"/>
+      <c r="A282" s="187"/>
       <c r="B282" s="188"/>
       <c r="C282" s="7" t="s">
         <v>11</v>
@@ -5923,7 +5931,7 @@
       <c r="I282" s="11"/>
     </row>
     <row r="283" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A283" s="216"/>
+      <c r="A283" s="187"/>
       <c r="B283" s="188"/>
       <c r="C283" s="7" t="s">
         <v>12</v>
@@ -5936,7 +5944,7 @@
       <c r="I283" s="11"/>
     </row>
     <row r="284" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A284" s="216"/>
+      <c r="A284" s="187"/>
       <c r="B284" s="188"/>
       <c r="C284" s="16" t="s">
         <v>1</v>
@@ -5949,7 +5957,7 @@
       <c r="I284" s="5"/>
     </row>
     <row r="285" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A285" s="216">
+      <c r="A285" s="187">
         <v>57</v>
       </c>
       <c r="B285" s="188"/>
@@ -5962,7 +5970,7 @@
       <c r="I285" s="20"/>
     </row>
     <row r="286" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A286" s="216"/>
+      <c r="A286" s="187"/>
       <c r="B286" s="188"/>
       <c r="C286" s="11"/>
       <c r="D286" s="10"/>
@@ -5973,7 +5981,7 @@
       <c r="I286" s="11"/>
     </row>
     <row r="287" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A287" s="216"/>
+      <c r="A287" s="187"/>
       <c r="B287" s="188"/>
       <c r="C287" s="7" t="s">
         <v>11</v>
@@ -5986,7 +5994,7 @@
       <c r="I287" s="11"/>
     </row>
     <row r="288" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A288" s="216"/>
+      <c r="A288" s="187"/>
       <c r="B288" s="188"/>
       <c r="C288" s="7" t="s">
         <v>12</v>
@@ -5999,7 +6007,7 @@
       <c r="I288" s="11"/>
     </row>
     <row r="289" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A289" s="216"/>
+      <c r="A289" s="187"/>
       <c r="B289" s="188"/>
       <c r="C289" s="16" t="s">
         <v>1</v>
@@ -6012,7 +6020,7 @@
       <c r="I289" s="5"/>
     </row>
     <row r="290" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A290" s="216">
+      <c r="A290" s="187">
         <v>58</v>
       </c>
       <c r="B290" s="188"/>
@@ -6025,7 +6033,7 @@
       <c r="I290" s="28"/>
     </row>
     <row r="291" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A291" s="216"/>
+      <c r="A291" s="187"/>
       <c r="B291" s="188"/>
       <c r="C291" s="11"/>
       <c r="D291" s="10"/>
@@ -6036,7 +6044,7 @@
       <c r="I291" s="14"/>
     </row>
     <row r="292" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A292" s="216"/>
+      <c r="A292" s="187"/>
       <c r="B292" s="188"/>
       <c r="C292" s="7" t="s">
         <v>11</v>
@@ -6049,7 +6057,7 @@
       <c r="I292" s="14"/>
     </row>
     <row r="293" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A293" s="216"/>
+      <c r="A293" s="187"/>
       <c r="B293" s="188"/>
       <c r="C293" s="7" t="s">
         <v>12</v>
@@ -6062,7 +6070,7 @@
       <c r="I293" s="14"/>
     </row>
     <row r="294" spans="1:9" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A294" s="216"/>
+      <c r="A294" s="187"/>
       <c r="B294" s="188"/>
       <c r="C294" s="16" t="s">
         <v>1</v>
@@ -6075,7 +6083,7 @@
       <c r="I294" s="5"/>
     </row>
     <row r="295" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A295" s="216">
+      <c r="A295" s="187">
         <v>59</v>
       </c>
       <c r="B295" s="188"/>
@@ -6088,7 +6096,7 @@
       <c r="I295" s="20"/>
     </row>
     <row r="296" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A296" s="216"/>
+      <c r="A296" s="187"/>
       <c r="B296" s="188"/>
       <c r="C296" s="11"/>
       <c r="D296" s="11"/>
@@ -6099,7 +6107,7 @@
       <c r="I296" s="11"/>
     </row>
     <row r="297" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A297" s="216"/>
+      <c r="A297" s="187"/>
       <c r="B297" s="188"/>
       <c r="C297" s="7" t="s">
         <v>11</v>
@@ -6112,7 +6120,7 @@
       <c r="I297" s="11"/>
     </row>
     <row r="298" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A298" s="216"/>
+      <c r="A298" s="187"/>
       <c r="B298" s="188"/>
       <c r="C298" s="7" t="s">
         <v>12</v>
@@ -6125,7 +6133,7 @@
       <c r="I298" s="11"/>
     </row>
     <row r="299" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A299" s="216"/>
+      <c r="A299" s="187"/>
       <c r="B299" s="188"/>
       <c r="C299" s="16" t="s">
         <v>1</v>
@@ -6138,7 +6146,7 @@
       <c r="I299" s="18"/>
     </row>
     <row r="300" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A300" s="216">
+      <c r="A300" s="187">
         <v>60</v>
       </c>
       <c r="B300" s="188"/>
@@ -6151,7 +6159,7 @@
       <c r="I300" s="20"/>
     </row>
     <row r="301" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A301" s="216"/>
+      <c r="A301" s="187"/>
       <c r="B301" s="188"/>
       <c r="C301" s="11"/>
       <c r="D301" s="11"/>
@@ -6162,7 +6170,7 @@
       <c r="I301" s="11"/>
     </row>
     <row r="302" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A302" s="216"/>
+      <c r="A302" s="187"/>
       <c r="B302" s="188"/>
       <c r="C302" s="7" t="s">
         <v>11</v>
@@ -6175,7 +6183,7 @@
       <c r="I302" s="11"/>
     </row>
     <row r="303" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A303" s="216"/>
+      <c r="A303" s="187"/>
       <c r="B303" s="188"/>
       <c r="C303" s="7" t="s">
         <v>12</v>
@@ -6188,7 +6196,7 @@
       <c r="I303" s="11"/>
     </row>
     <row r="304" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A304" s="216"/>
+      <c r="A304" s="187"/>
       <c r="B304" s="188"/>
       <c r="C304" s="16" t="s">
         <v>1</v>
@@ -6201,7 +6209,7 @@
       <c r="I304" s="5"/>
     </row>
     <row r="305" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A305" s="216">
+      <c r="A305" s="187">
         <v>61</v>
       </c>
       <c r="B305" s="188"/>
@@ -6214,7 +6222,7 @@
       <c r="I305" s="21"/>
     </row>
     <row r="306" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A306" s="216"/>
+      <c r="A306" s="187"/>
       <c r="B306" s="188"/>
       <c r="C306" s="11"/>
       <c r="D306" s="11"/>
@@ -6225,7 +6233,7 @@
       <c r="I306" s="10"/>
     </row>
     <row r="307" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A307" s="216"/>
+      <c r="A307" s="187"/>
       <c r="B307" s="188"/>
       <c r="C307" s="7" t="s">
         <v>11</v>
@@ -6238,7 +6246,7 @@
       <c r="I307" s="10"/>
     </row>
     <row r="308" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A308" s="216"/>
+      <c r="A308" s="187"/>
       <c r="B308" s="188"/>
       <c r="C308" s="7" t="s">
         <v>12</v>
@@ -6251,7 +6259,7 @@
       <c r="I308" s="10"/>
     </row>
     <row r="309" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A309" s="216"/>
+      <c r="A309" s="187"/>
       <c r="B309" s="188"/>
       <c r="C309" s="16" t="s">
         <v>1</v>
@@ -6264,7 +6272,7 @@
       <c r="I309" s="18"/>
     </row>
     <row r="310" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A310" s="216">
+      <c r="A310" s="187">
         <v>62</v>
       </c>
       <c r="B310" s="188"/>
@@ -6277,7 +6285,7 @@
       <c r="I310" s="20"/>
     </row>
     <row r="311" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A311" s="216"/>
+      <c r="A311" s="187"/>
       <c r="B311" s="188"/>
       <c r="C311" s="11"/>
       <c r="D311" s="15"/>
@@ -6288,7 +6296,7 @@
       <c r="I311" s="11"/>
     </row>
     <row r="312" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A312" s="216"/>
+      <c r="A312" s="187"/>
       <c r="B312" s="188"/>
       <c r="C312" s="7" t="s">
         <v>11</v>
@@ -6301,7 +6309,7 @@
       <c r="I312" s="11"/>
     </row>
     <row r="313" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A313" s="216"/>
+      <c r="A313" s="187"/>
       <c r="B313" s="188"/>
       <c r="C313" s="7" t="s">
         <v>12</v>
@@ -6314,7 +6322,7 @@
       <c r="I313" s="11"/>
     </row>
     <row r="314" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A314" s="216"/>
+      <c r="A314" s="187"/>
       <c r="B314" s="188"/>
       <c r="C314" s="16" t="s">
         <v>1</v>
@@ -6327,7 +6335,7 @@
       <c r="I314" s="18"/>
     </row>
     <row r="315" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A315" s="216">
+      <c r="A315" s="187">
         <v>63</v>
       </c>
       <c r="B315" s="188"/>
@@ -6340,7 +6348,7 @@
       <c r="I315" s="20"/>
     </row>
     <row r="316" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A316" s="216"/>
+      <c r="A316" s="187"/>
       <c r="B316" s="188"/>
       <c r="C316" s="11"/>
       <c r="D316" s="11"/>
@@ -6351,7 +6359,7 @@
       <c r="I316" s="11"/>
     </row>
     <row r="317" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A317" s="216"/>
+      <c r="A317" s="187"/>
       <c r="B317" s="188"/>
       <c r="C317" s="7" t="s">
         <v>11</v>
@@ -6364,7 +6372,7 @@
       <c r="I317" s="11"/>
     </row>
     <row r="318" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A318" s="216"/>
+      <c r="A318" s="187"/>
       <c r="B318" s="188"/>
       <c r="C318" s="7" t="s">
         <v>12</v>
@@ -6377,7 +6385,7 @@
       <c r="I318" s="11"/>
     </row>
     <row r="319" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A319" s="216"/>
+      <c r="A319" s="187"/>
       <c r="B319" s="188"/>
       <c r="C319" s="24" t="s">
         <v>1</v>
@@ -6390,7 +6398,7 @@
       <c r="I319" s="26"/>
     </row>
     <row r="320" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A320" s="216">
+      <c r="A320" s="187">
         <v>64</v>
       </c>
       <c r="B320" s="188"/>
@@ -6403,7 +6411,7 @@
       <c r="I320" s="4"/>
     </row>
     <row r="321" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A321" s="216"/>
+      <c r="A321" s="187"/>
       <c r="B321" s="188"/>
       <c r="C321" s="11"/>
       <c r="D321" s="11"/>
@@ -6414,7 +6422,7 @@
       <c r="I321" s="11"/>
     </row>
     <row r="322" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A322" s="216"/>
+      <c r="A322" s="187"/>
       <c r="B322" s="188"/>
       <c r="C322" s="7" t="s">
         <v>11</v>
@@ -6427,7 +6435,7 @@
       <c r="I322" s="11"/>
     </row>
     <row r="323" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A323" s="216"/>
+      <c r="A323" s="187"/>
       <c r="B323" s="188"/>
       <c r="C323" s="7" t="s">
         <v>12</v>
@@ -6440,7 +6448,7 @@
       <c r="I323" s="11"/>
     </row>
     <row r="324" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A324" s="216"/>
+      <c r="A324" s="187"/>
       <c r="B324" s="188"/>
       <c r="C324" s="16" t="s">
         <v>1</v>
@@ -6453,7 +6461,7 @@
       <c r="I324" s="5"/>
     </row>
     <row r="325" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A325" s="216">
+      <c r="A325" s="187">
         <v>65</v>
       </c>
       <c r="B325" s="188"/>
@@ -6466,7 +6474,7 @@
       <c r="I325" s="33"/>
     </row>
     <row r="326" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A326" s="216"/>
+      <c r="A326" s="187"/>
       <c r="B326" s="188"/>
       <c r="C326" s="11"/>
       <c r="D326" s="11"/>
@@ -6477,7 +6485,7 @@
       <c r="I326" s="11"/>
     </row>
     <row r="327" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A327" s="216"/>
+      <c r="A327" s="187"/>
       <c r="B327" s="188"/>
       <c r="C327" s="7" t="s">
         <v>11</v>
@@ -6490,7 +6498,7 @@
       <c r="I327" s="11"/>
     </row>
     <row r="328" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A328" s="216"/>
+      <c r="A328" s="187"/>
       <c r="B328" s="188"/>
       <c r="C328" s="7" t="s">
         <v>12</v>
@@ -6503,7 +6511,7 @@
       <c r="I328" s="11"/>
     </row>
     <row r="329" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A329" s="216"/>
+      <c r="A329" s="187"/>
       <c r="B329" s="188"/>
       <c r="C329" s="31" t="s">
         <v>1</v>
@@ -6539,59 +6547,66 @@
     <row r="351" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="352" ht="18.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="135">
-    <mergeCell ref="A325:A329"/>
-    <mergeCell ref="B325:B329"/>
-    <mergeCell ref="A310:A314"/>
-    <mergeCell ref="B310:B314"/>
-    <mergeCell ref="A315:A319"/>
-    <mergeCell ref="B315:B319"/>
-    <mergeCell ref="A320:A324"/>
-    <mergeCell ref="B320:B324"/>
-    <mergeCell ref="A295:A299"/>
-    <mergeCell ref="B295:B299"/>
-    <mergeCell ref="A300:A304"/>
-    <mergeCell ref="B300:B304"/>
-    <mergeCell ref="A305:A309"/>
-    <mergeCell ref="B305:B309"/>
-    <mergeCell ref="A280:A284"/>
-    <mergeCell ref="B280:B284"/>
-    <mergeCell ref="A285:A289"/>
-    <mergeCell ref="B285:B289"/>
-    <mergeCell ref="A290:A294"/>
-    <mergeCell ref="B290:B294"/>
-    <mergeCell ref="A265:A269"/>
-    <mergeCell ref="B265:B269"/>
-    <mergeCell ref="A270:A274"/>
-    <mergeCell ref="B270:B274"/>
-    <mergeCell ref="A275:A279"/>
-    <mergeCell ref="B275:B279"/>
-    <mergeCell ref="A250:A254"/>
-    <mergeCell ref="B250:B254"/>
-    <mergeCell ref="A255:A259"/>
-    <mergeCell ref="B255:B259"/>
-    <mergeCell ref="A260:A264"/>
-    <mergeCell ref="B260:B264"/>
-    <mergeCell ref="A235:A239"/>
-    <mergeCell ref="B235:B239"/>
-    <mergeCell ref="A240:A244"/>
-    <mergeCell ref="B240:B244"/>
-    <mergeCell ref="A245:A249"/>
-    <mergeCell ref="B245:B249"/>
-    <mergeCell ref="B180:B184"/>
-    <mergeCell ref="A175:A179"/>
-    <mergeCell ref="A220:A224"/>
-    <mergeCell ref="B220:B224"/>
-    <mergeCell ref="A225:A229"/>
-    <mergeCell ref="B225:B229"/>
-    <mergeCell ref="A230:A234"/>
-    <mergeCell ref="B230:B234"/>
-    <mergeCell ref="A205:A209"/>
-    <mergeCell ref="B205:B209"/>
-    <mergeCell ref="A210:A214"/>
-    <mergeCell ref="B210:B214"/>
-    <mergeCell ref="A215:A219"/>
-    <mergeCell ref="B215:B219"/>
+  <mergeCells count="136">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="B145:B149"/>
+    <mergeCell ref="A110:A114"/>
+    <mergeCell ref="B110:B114"/>
+    <mergeCell ref="A85:A89"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="B35:B39"/>
+    <mergeCell ref="A35:A39"/>
+    <mergeCell ref="A45:A49"/>
+    <mergeCell ref="B10:B14"/>
+    <mergeCell ref="A10:A14"/>
+    <mergeCell ref="A30:A34"/>
+    <mergeCell ref="B30:B34"/>
+    <mergeCell ref="A25:A29"/>
+    <mergeCell ref="B25:B29"/>
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="B20:B24"/>
+    <mergeCell ref="A70:A74"/>
+    <mergeCell ref="B70:B74"/>
+    <mergeCell ref="A75:A79"/>
+    <mergeCell ref="B75:B79"/>
+    <mergeCell ref="A170:A174"/>
+    <mergeCell ref="B170:B174"/>
+    <mergeCell ref="A140:A144"/>
+    <mergeCell ref="B140:B144"/>
+    <mergeCell ref="A135:A139"/>
+    <mergeCell ref="B135:B139"/>
+    <mergeCell ref="A130:A134"/>
+    <mergeCell ref="B130:B134"/>
+    <mergeCell ref="A125:A129"/>
+    <mergeCell ref="B125:B129"/>
+    <mergeCell ref="A120:A124"/>
+    <mergeCell ref="B120:B124"/>
+    <mergeCell ref="A115:A119"/>
+    <mergeCell ref="B115:B119"/>
+    <mergeCell ref="A15:A19"/>
+    <mergeCell ref="B15:B19"/>
+    <mergeCell ref="B85:B89"/>
+    <mergeCell ref="A100:A104"/>
+    <mergeCell ref="B100:B104"/>
+    <mergeCell ref="A5:A9"/>
+    <mergeCell ref="B5:B9"/>
+    <mergeCell ref="B45:B49"/>
+    <mergeCell ref="A145:A149"/>
+    <mergeCell ref="A105:A109"/>
+    <mergeCell ref="B105:B109"/>
+    <mergeCell ref="B80:B84"/>
+    <mergeCell ref="A80:A84"/>
+    <mergeCell ref="A90:A94"/>
+    <mergeCell ref="B90:B94"/>
+    <mergeCell ref="A95:A99"/>
+    <mergeCell ref="B95:B99"/>
+    <mergeCell ref="A50:A54"/>
+    <mergeCell ref="A55:A59"/>
+    <mergeCell ref="B50:B54"/>
     <mergeCell ref="A40:A44"/>
     <mergeCell ref="B40:B44"/>
     <mergeCell ref="A195:A199"/>
@@ -6616,65 +6631,59 @@
     <mergeCell ref="A185:A189"/>
     <mergeCell ref="B185:B189"/>
     <mergeCell ref="A180:A184"/>
-    <mergeCell ref="A105:A109"/>
-    <mergeCell ref="B105:B109"/>
-    <mergeCell ref="B80:B84"/>
-    <mergeCell ref="A80:A84"/>
-    <mergeCell ref="A90:A94"/>
-    <mergeCell ref="B90:B94"/>
-    <mergeCell ref="A95:A99"/>
-    <mergeCell ref="B95:B99"/>
-    <mergeCell ref="A50:A54"/>
-    <mergeCell ref="A55:A59"/>
-    <mergeCell ref="B50:B54"/>
+    <mergeCell ref="B180:B184"/>
+    <mergeCell ref="A175:A179"/>
+    <mergeCell ref="A220:A224"/>
+    <mergeCell ref="B220:B224"/>
+    <mergeCell ref="A225:A229"/>
+    <mergeCell ref="B225:B229"/>
+    <mergeCell ref="A230:A234"/>
+    <mergeCell ref="B230:B234"/>
+    <mergeCell ref="A205:A209"/>
+    <mergeCell ref="B205:B209"/>
+    <mergeCell ref="A210:A214"/>
+    <mergeCell ref="B210:B214"/>
+    <mergeCell ref="A215:A219"/>
+    <mergeCell ref="B215:B219"/>
     <mergeCell ref="B175:B179"/>
-    <mergeCell ref="A170:A174"/>
-    <mergeCell ref="B170:B174"/>
-    <mergeCell ref="A1:I2"/>
-    <mergeCell ref="A140:A144"/>
-    <mergeCell ref="B140:B144"/>
-    <mergeCell ref="A135:A139"/>
-    <mergeCell ref="B135:B139"/>
-    <mergeCell ref="A130:A134"/>
-    <mergeCell ref="B130:B134"/>
-    <mergeCell ref="A125:A129"/>
-    <mergeCell ref="B125:B129"/>
-    <mergeCell ref="A120:A124"/>
-    <mergeCell ref="B120:B124"/>
-    <mergeCell ref="A115:A119"/>
-    <mergeCell ref="B115:B119"/>
-    <mergeCell ref="A15:A19"/>
-    <mergeCell ref="B15:B19"/>
-    <mergeCell ref="B85:B89"/>
-    <mergeCell ref="A100:A104"/>
-    <mergeCell ref="B100:B104"/>
-    <mergeCell ref="A5:A9"/>
-    <mergeCell ref="B5:B9"/>
-    <mergeCell ref="B45:B49"/>
-    <mergeCell ref="A145:A149"/>
-    <mergeCell ref="B145:B149"/>
-    <mergeCell ref="A110:A114"/>
-    <mergeCell ref="B110:B114"/>
-    <mergeCell ref="A85:A89"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="B35:B39"/>
-    <mergeCell ref="A35:A39"/>
-    <mergeCell ref="A45:A49"/>
-    <mergeCell ref="B10:B14"/>
-    <mergeCell ref="A10:A14"/>
-    <mergeCell ref="A30:A34"/>
-    <mergeCell ref="B30:B34"/>
-    <mergeCell ref="A25:A29"/>
-    <mergeCell ref="B25:B29"/>
-    <mergeCell ref="A20:A24"/>
-    <mergeCell ref="B20:B24"/>
-    <mergeCell ref="A70:A74"/>
-    <mergeCell ref="B70:B74"/>
-    <mergeCell ref="A75:A79"/>
-    <mergeCell ref="B75:B79"/>
+    <mergeCell ref="A250:A254"/>
+    <mergeCell ref="B250:B254"/>
+    <mergeCell ref="A255:A259"/>
+    <mergeCell ref="B255:B259"/>
+    <mergeCell ref="A260:A264"/>
+    <mergeCell ref="B260:B264"/>
+    <mergeCell ref="A235:A239"/>
+    <mergeCell ref="B235:B239"/>
+    <mergeCell ref="A240:A244"/>
+    <mergeCell ref="B240:B244"/>
+    <mergeCell ref="A245:A249"/>
+    <mergeCell ref="B245:B249"/>
+    <mergeCell ref="A280:A284"/>
+    <mergeCell ref="B280:B284"/>
+    <mergeCell ref="A285:A289"/>
+    <mergeCell ref="B285:B289"/>
+    <mergeCell ref="A290:A294"/>
+    <mergeCell ref="B290:B294"/>
+    <mergeCell ref="A265:A269"/>
+    <mergeCell ref="B265:B269"/>
+    <mergeCell ref="A270:A274"/>
+    <mergeCell ref="B270:B274"/>
+    <mergeCell ref="A275:A279"/>
+    <mergeCell ref="B275:B279"/>
+    <mergeCell ref="A325:A329"/>
+    <mergeCell ref="B325:B329"/>
+    <mergeCell ref="A310:A314"/>
+    <mergeCell ref="B310:B314"/>
+    <mergeCell ref="A315:A319"/>
+    <mergeCell ref="B315:B319"/>
+    <mergeCell ref="A320:A324"/>
+    <mergeCell ref="B320:B324"/>
+    <mergeCell ref="A295:A299"/>
+    <mergeCell ref="B295:B299"/>
+    <mergeCell ref="A300:A304"/>
+    <mergeCell ref="B300:B304"/>
+    <mergeCell ref="A305:A309"/>
+    <mergeCell ref="B305:B309"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="73" fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -6687,6 +6696,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e2d4777c-c384-4cb0-8366-9c9ca00b276c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="95d38b54-3432-49bd-ac39-53ac5399fed4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F6C9734486F8704886AB210B4CB8A822" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="91ee5eb64b491139767e4dc61b3ecc65">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e2d4777c-c384-4cb0-8366-9c9ca00b276c" xmlns:ns3="95d38b54-3432-49bd-ac39-53ac5399fed4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a63b6cccca0a6e56e26ad9374b9f7462" ns2:_="" ns3:_="">
     <xsd:import namespace="e2d4777c-c384-4cb0-8366-9c9ca00b276c"/>
@@ -6893,27 +6922,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F850EB7-2AC2-49C0-BD0F-12B1AFA084A2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="95d38b54-3432-49bd-ac39-53ac5399fed4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="e2d4777c-c384-4cb0-8366-9c9ca00b276c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e2d4777c-c384-4cb0-8366-9c9ca00b276c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="95d38b54-3432-49bd-ac39-53ac5399fed4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E66689E8-59E2-4C97-BE96-1ABF2AD0207B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A19570C-2662-4116-BA7A-790BC715D51A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6930,29 +6964,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E66689E8-59E2-4C97-BE96-1ABF2AD0207B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F850EB7-2AC2-49C0-BD0F-12B1AFA084A2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="95d38b54-3432-49bd-ac39-53ac5399fed4"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="e2d4777c-c384-4cb0-8366-9c9ca00b276c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>